--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -81,16 +81,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100548298</t>
+          <t xml:space="preserve">100280264, 100280269, 100280265, 100280266, 100280268</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F2">
-        <v>450</v>
+        <v>36105</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -131,12 +131,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463273</t>
+          <t xml:space="preserve">100548298</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F3">
@@ -181,7 +181,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">321593, 321594, 321595</t>
+          <t xml:space="preserve">1463273</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -190,7 +190,7 @@
         </is>
       </c>
       <c r="F4">
-        <v>3496</v>
+        <v>450</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -231,16 +231,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268440</t>
+          <t xml:space="preserve">321593, 321594, 321595</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F5">
-        <v>458</v>
+        <v>3496</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -281,16 +281,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">4273040</t>
+          <t xml:space="preserve">322540, 322541</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F6">
-        <v>455</v>
+        <v>9459</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -331,16 +331,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287946</t>
+          <t xml:space="preserve">323774, 323775, 323776</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F7">
-        <v>1235</v>
+        <v>1533</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -381,7 +381,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293717</t>
+          <t xml:space="preserve">324132, 324133</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -390,7 +390,7 @@
         </is>
       </c>
       <c r="F8">
-        <v>502</v>
+        <v>1473</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -431,16 +431,16 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">4297715</t>
+          <t xml:space="preserve">325727, 325728</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F9">
-        <v>3047</v>
+        <v>2343</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -481,16 +481,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298855</t>
+          <t xml:space="preserve">325727, 325728</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F10">
-        <v>450</v>
+        <v>352</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -531,16 +531,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298855</t>
+          <t xml:space="preserve">325727, 325728</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F11">
-        <v>407</v>
+        <v>352</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -581,16 +581,16 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301495</t>
+          <t xml:space="preserve">331936, 331937</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F12">
-        <v>298</v>
+        <v>6602</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -631,16 +631,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301565</t>
+          <t xml:space="preserve">332890, 332891</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F13">
-        <v>458</v>
+        <v>3476</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -681,16 +681,16 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301650</t>
+          <t xml:space="preserve">333777, 333778</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F14">
-        <v>1139</v>
+        <v>2559</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -731,16 +731,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">4327537</t>
+          <t xml:space="preserve">408943, 408944</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F15">
-        <v>1266</v>
+        <v>11768</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4337482</t>
+          <t xml:space="preserve">4268440</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F16">
-        <v>271</v>
+        <v>458</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -831,16 +831,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339669</t>
+          <t xml:space="preserve">4273040</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F17">
-        <v>1299</v>
+        <v>455</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -881,16 +881,16 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339669</t>
+          <t xml:space="preserve">4287946</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F18">
-        <v>280</v>
+        <v>1235</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339669</t>
+          <t xml:space="preserve">4293717</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F19">
-        <v>1320</v>
+        <v>502</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -981,16 +981,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339928</t>
+          <t xml:space="preserve">4298855</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F20">
-        <v>524</v>
+        <v>450</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">5637741</t>
+          <t xml:space="preserve">4298855</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F21">
-        <v>998</v>
+        <v>407</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1081,16 +1081,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">5641335</t>
+          <t xml:space="preserve">4337482</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F22">
-        <v>998</v>
+        <v>271</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1131,16 +1131,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642082</t>
+          <t xml:space="preserve">4339928</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F23">
-        <v>335</v>
+        <v>524</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">5637741</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F24">
-        <v>2345</v>
+        <v>998</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1231,16 +1231,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">5641335</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F25">
-        <v>2962</v>
+        <v>998</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1281,16 +1281,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646746</t>
+          <t xml:space="preserve">5642082</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F26">
-        <v>2801</v>
+        <v>335</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1331,16 +1331,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646746</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F27">
-        <v>1051</v>
+        <v>2345</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1381,16 +1381,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F28">
-        <v>539</v>
+        <v>2962</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,16 +1431,16 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">5646746</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F29">
-        <v>591</v>
+        <v>2801</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1481,16 +1481,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">5646746</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F30">
-        <v>517</v>
+        <v>1051</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1536,11 +1536,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F31">
-        <v>1811</v>
+        <v>539</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646875</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>1251</v>
+        <v>591</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1631,16 +1631,16 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647421</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F33">
-        <v>276</v>
+        <v>517</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">7084738</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F34">
-        <v>273</v>
+        <v>1811</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1731,16 +1731,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">738303, 5644002</t>
+          <t xml:space="preserve">5647421</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F35">
-        <v>1039</v>
+        <v>276</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">738317, 4337482</t>
+          <t xml:space="preserve">7084738</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F36">
-        <v>816</v>
+        <v>273</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">738335, 4327352</t>
+          <t xml:space="preserve">738303, 5644002</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>715</v>
+        <v>1039</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">738358, 8843882</t>
+          <t xml:space="preserve">738317, 4337482</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>1240</v>
+        <v>816</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1936,11 +1936,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F39">
-        <v>602</v>
+        <v>1240</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">738371, 4339668</t>
+          <t xml:space="preserve">738358, 8843882</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F40">
-        <v>1200</v>
+        <v>602</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2031,16 +2031,16 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">738401, 5646176</t>
+          <t xml:space="preserve">738371, 4339668</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F41">
-        <v>394</v>
+        <v>1200</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2081,16 +2081,16 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">738434, 4268923</t>
+          <t xml:space="preserve">738401, 5646176</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F42">
-        <v>460</v>
+        <v>394</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2131,16 +2131,16 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">738445, 9962230</t>
+          <t xml:space="preserve">738434, 4268923</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F43">
-        <v>1206</v>
+        <v>460</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2181,16 +2181,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">738514, 5646746</t>
+          <t xml:space="preserve">738445, 9962230</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F44">
-        <v>255</v>
+        <v>1206</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2231,16 +2231,16 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831513</t>
+          <t xml:space="preserve">738514, 5646746</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F45">
-        <v>550</v>
+        <v>255</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2281,16 +2281,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831521</t>
+          <t xml:space="preserve">8831513</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F46">
-        <v>705</v>
+        <v>550</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2336,11 +2336,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F47">
-        <v>1098</v>
+        <v>705</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2386,11 +2386,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F48">
-        <v>1452</v>
+        <v>1098</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2431,16 +2431,16 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831643</t>
+          <t xml:space="preserve">8831521</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F49">
-        <v>1841</v>
+        <v>1452</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2481,16 +2481,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031557</t>
+          <t xml:space="preserve">8831643</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F50">
-        <v>853</v>
+        <v>1841</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2531,30 +2531,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287793</t>
+          <t xml:space="preserve">9031557</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F51">
-        <v>311</v>
+        <v>853</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">200005814</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-04-29</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2581,25 +2581,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">9683312</t>
+          <t xml:space="preserve">4301565</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F52">
-        <v>1262</v>
+        <v>458</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200006369</t>
+          <t xml:space="preserve">200004055</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-06-16</t>
+          <t xml:space="preserve">2017-12-18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2631,25 +2631,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">4287793</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F53">
-        <v>1920</v>
+        <v>311</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200007213</t>
+          <t xml:space="preserve">200005814</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-08-19</t>
+          <t xml:space="preserve">2018-04-29</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4296269</t>
+          <t xml:space="preserve">9683312</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2690,16 +2690,16 @@
         </is>
       </c>
       <c r="F54">
-        <v>744</v>
+        <v>1262</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019232</t>
+          <t xml:space="preserve">200006369</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2018-06-16</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2731,25 +2731,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F55">
-        <v>1378</v>
+        <v>1920</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025850</t>
+          <t xml:space="preserve">200007213</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-18</t>
+          <t xml:space="preserve">2018-08-19</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">100020899</t>
+          <t xml:space="preserve">738335, 4327352</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2790,16 +2790,16 @@
         </is>
       </c>
       <c r="F56">
-        <v>1296</v>
+        <v>715</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032357</t>
+          <t xml:space="preserve">200014768</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-08</t>
+          <t xml:space="preserve">2019-06-10</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642094</t>
+          <t xml:space="preserve">4296269</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2840,16 +2840,16 @@
         </is>
       </c>
       <c r="F57">
-        <v>701</v>
+        <v>744</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032602</t>
+          <t xml:space="preserve">200019232</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-15</t>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287946</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2890,16 +2890,16 @@
         </is>
       </c>
       <c r="F58">
-        <v>2266</v>
+        <v>1378</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047462</t>
+          <t xml:space="preserve">200025850</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-31</t>
+          <t xml:space="preserve">2019-12-18</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">7895719</t>
+          <t xml:space="preserve">100020899</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2940,16 +2940,16 @@
         </is>
       </c>
       <c r="F59">
-        <v>273</v>
+        <v>1296</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100217499</t>
+          <t xml:space="preserve">200032357</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-14</t>
+          <t xml:space="preserve">2020-06-08</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -2981,25 +2981,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463870</t>
+          <t xml:space="preserve">5642094</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F60">
-        <v>3185</v>
+        <v>701</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049551</t>
+          <t xml:space="preserve">200032602</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2020-06-15</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8742377</t>
+          <t xml:space="preserve">4287946</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3040,16 +3040,16 @@
         </is>
       </c>
       <c r="F61">
-        <v>3617</v>
+        <v>2266</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050729</t>
+          <t xml:space="preserve">200047462</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-28</t>
+          <t xml:space="preserve">2021-03-31</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">324132, 324133</t>
+          <t xml:space="preserve">7895719</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="F62">
-        <v>1473</v>
+        <v>273</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052534</t>
+          <t xml:space="preserve">100217499</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-01</t>
+          <t xml:space="preserve">2021-04-14</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3131,25 +3131,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301495</t>
+          <t xml:space="preserve">1463870</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F63">
-        <v>2844</v>
+        <v>3185</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053167</t>
+          <t xml:space="preserve">200049551</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-22</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">7750871</t>
+          <t xml:space="preserve">8742377</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3190,16 +3190,16 @@
         </is>
       </c>
       <c r="F64">
-        <v>1254</v>
+        <v>3617</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053158</t>
+          <t xml:space="preserve">200050729</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-22</t>
+          <t xml:space="preserve">2021-06-28</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3236,15 +3236,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F65">
-        <v>2522</v>
+        <v>1254</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053159</t>
+          <t xml:space="preserve">200053157</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3281,25 +3281,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">325727, 325728</t>
+          <t xml:space="preserve">7750871</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F66">
-        <v>2343</v>
+        <v>2522</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053294</t>
+          <t xml:space="preserve">200053157</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-27</t>
+          <t xml:space="preserve">2021-09-22</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3331,25 +3331,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">325727, 325728</t>
+          <t xml:space="preserve">5646862</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F67">
-        <v>352</v>
+        <v>1169</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053294</t>
+          <t xml:space="preserve">200053806</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-27</t>
+          <t xml:space="preserve">2021-10-12</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3381,25 +3381,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">325727, 325728</t>
+          <t xml:space="preserve">4297715</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F68">
-        <v>352</v>
+        <v>3047</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053294</t>
+          <t xml:space="preserve">200056422</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-27</t>
+          <t xml:space="preserve">2022-01-03</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3431,25 +3431,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646862</t>
+          <t xml:space="preserve">5643101</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F69">
-        <v>1169</v>
+        <v>572</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053806</t>
+          <t xml:space="preserve">200057417</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-12</t>
+          <t xml:space="preserve">2022-02-14</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3481,25 +3481,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5643101</t>
+          <t xml:space="preserve">8194376</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F70">
-        <v>572</v>
+        <v>1844</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057417</t>
+          <t xml:space="preserve">310004216</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-14</t>
+          <t xml:space="preserve">2022-09-13</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3531,25 +3531,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194376</t>
+          <t xml:space="preserve">4292353</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F71">
-        <v>1844</v>
+        <v>464</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">310004216</t>
+          <t xml:space="preserve">310006732</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-09-13</t>
+          <t xml:space="preserve">2022-10-01</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3586,11 +3586,11 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F72">
-        <v>464</v>
+        <v>261</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3631,25 +3631,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4292353</t>
+          <t xml:space="preserve">7735835</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F73">
-        <v>261</v>
+        <v>1003</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">310006732</t>
+          <t xml:space="preserve">310013380</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-10-01</t>
+          <t xml:space="preserve">2022-11-14</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3681,25 +3681,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">7735835</t>
+          <t xml:space="preserve">5647450</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F74">
-        <v>1003</v>
+        <v>266</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013380</t>
+          <t xml:space="preserve">310015648</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-14</t>
+          <t xml:space="preserve">2022-11-30</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3731,25 +3731,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647450</t>
+          <t xml:space="preserve">4339669</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F75">
-        <v>266</v>
+        <v>1299</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">310015648</t>
+          <t xml:space="preserve">310035291</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-30</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3781,25 +3781,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301650</t>
+          <t xml:space="preserve">4339669</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F76">
-        <v>1231</v>
+        <v>280</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">310033398</t>
+          <t xml:space="preserve">310035291</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-04</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3831,25 +3831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642531</t>
+          <t xml:space="preserve">4339669</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F77">
-        <v>3753</v>
+        <v>1320</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">310037158</t>
+          <t xml:space="preserve">310035291</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-29</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3881,25 +3881,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301856</t>
+          <t xml:space="preserve">5642531</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F78">
-        <v>2172</v>
+        <v>3753</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053869</t>
+          <t xml:space="preserve">310037158</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-13</t>
+          <t xml:space="preserve">2023-04-29</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3931,25 +3931,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061763</t>
+          <t xml:space="preserve">4301856</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F79">
-        <v>875</v>
+        <v>2172</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311056702</t>
+          <t xml:space="preserve">311053859</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-28</t>
+          <t xml:space="preserve">2024-05-13</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3981,25 +3981,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">100061763</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F80">
-        <v>10244</v>
+        <v>875</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084316</t>
+          <t xml:space="preserve">311056702</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-20</t>
+          <t xml:space="preserve">2024-05-28</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8059978</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="F81">
-        <v>438</v>
+        <v>10244</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109196</t>
+          <t xml:space="preserve">311084316</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-27</t>
+          <t xml:space="preserve">2024-11-20</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">4297975</t>
+          <t xml:space="preserve">8059978</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4090,16 +4090,16 @@
         </is>
       </c>
       <c r="F82">
-        <v>251</v>
+        <v>438</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110012</t>
+          <t xml:space="preserve">311109196</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-30</t>
+          <t xml:space="preserve">2025-04-27</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4131,20 +4131,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7735835</t>
+          <t xml:space="preserve">4297975</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F83">
-        <v>969</v>
+        <v>251</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110021</t>
+          <t xml:space="preserve">311110012</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">4294467</t>
+          <t xml:space="preserve">7735835</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F84">
-        <v>307</v>
+        <v>969</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311111614</t>
+          <t xml:space="preserve">311110021</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-08</t>
+          <t xml:space="preserve">2025-04-30</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335669</t>
+          <t xml:space="preserve">4294467</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="F85">
-        <v>720</v>
+        <v>307</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311114539</t>
+          <t xml:space="preserve">311111614</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-22</t>
+          <t xml:space="preserve">2025-05-08</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335670</t>
+          <t xml:space="preserve">4335669</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4290,11 +4290,11 @@
         </is>
       </c>
       <c r="F86">
-        <v>521</v>
+        <v>720</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311114537</t>
+          <t xml:space="preserve">311114539</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293691</t>
+          <t xml:space="preserve">4335670</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="F87">
-        <v>400</v>
+        <v>521</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311114922</t>
+          <t xml:space="preserve">311114537</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-05-22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4381,25 +4381,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">9438924</t>
+          <t xml:space="preserve">4293691</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F88">
-        <v>839</v>
+        <v>400</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115261</t>
+          <t xml:space="preserve">311114922</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-27</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4431,25 +4431,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">7084738</t>
+          <t xml:space="preserve">9438924</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F89">
-        <v>346</v>
+        <v>839</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115807</t>
+          <t xml:space="preserve">311115261</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-29</t>
+          <t xml:space="preserve">2025-05-27</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4486,11 +4486,11 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F90">
-        <v>389</v>
+        <v>346</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4531,25 +4531,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4296670</t>
+          <t xml:space="preserve">7084738</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F91">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118783</t>
+          <t xml:space="preserve">311115807</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-12</t>
+          <t xml:space="preserve">2025-05-29</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8742451</t>
+          <t xml:space="preserve">4296670</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -4590,11 +4590,11 @@
         </is>
       </c>
       <c r="F92">
-        <v>333</v>
+        <v>423</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118789</t>
+          <t xml:space="preserve">311118783</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">9683772</t>
+          <t xml:space="preserve">8742451</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -4640,16 +4640,16 @@
         </is>
       </c>
       <c r="F93">
-        <v>690</v>
+        <v>333</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311119427</t>
+          <t xml:space="preserve">311118789</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-16</t>
+          <t xml:space="preserve">2025-06-12</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268541</t>
+          <t xml:space="preserve">9683772</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4690,16 +4690,16 @@
         </is>
       </c>
       <c r="F94">
-        <v>913</v>
+        <v>690</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311119613</t>
+          <t xml:space="preserve">311119427</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-17</t>
+          <t xml:space="preserve">2025-06-16</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4296242</t>
+          <t xml:space="preserve">4268541</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4740,11 +4740,11 @@
         </is>
       </c>
       <c r="F95">
-        <v>330</v>
+        <v>913</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311119615</t>
+          <t xml:space="preserve">311119613</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268442</t>
+          <t xml:space="preserve">4296242</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -4790,16 +4790,16 @@
         </is>
       </c>
       <c r="F96">
-        <v>3440</v>
+        <v>330</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127901</t>
+          <t xml:space="preserve">311119615</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-06</t>
+          <t xml:space="preserve">2025-06-17</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4328112</t>
+          <t xml:space="preserve">4268442</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4840,11 +4840,11 @@
         </is>
       </c>
       <c r="F97">
-        <v>1364</v>
+        <v>3440</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127900</t>
+          <t xml:space="preserve">311127901</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640272</t>
+          <t xml:space="preserve">4328112</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4890,11 +4890,11 @@
         </is>
       </c>
       <c r="F98">
-        <v>558</v>
+        <v>1364</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127895</t>
+          <t xml:space="preserve">311127900</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5637904</t>
+          <t xml:space="preserve">5640272</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4940,16 +4940,16 @@
         </is>
       </c>
       <c r="F99">
-        <v>523</v>
+        <v>558</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311128478</t>
+          <t xml:space="preserve">311127895</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-11</t>
+          <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640416</t>
+          <t xml:space="preserve">5637904</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="F100">
-        <v>1125</v>
+        <v>523</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311130610</t>
+          <t xml:space="preserve">311128478</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-24</t>
+          <t xml:space="preserve">2025-08-11</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335210</t>
+          <t xml:space="preserve">5640416</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5040,16 +5040,16 @@
         </is>
       </c>
       <c r="F101">
-        <v>340</v>
+        <v>1125</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132329</t>
+          <t xml:space="preserve">311130610</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2025-08-24</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291207</t>
+          <t xml:space="preserve">4335210</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="F102">
-        <v>386</v>
+        <v>340</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311134644</t>
+          <t xml:space="preserve">311132329</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-15</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">9092406</t>
+          <t xml:space="preserve">4291207</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5140,16 +5140,16 @@
         </is>
       </c>
       <c r="F103">
-        <v>4837</v>
+        <v>386</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311151610</t>
+          <t xml:space="preserve">311134644</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-22</t>
+          <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850144</t>
+          <t xml:space="preserve">9092406</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5190,16 +5190,16 @@
         </is>
       </c>
       <c r="F104">
-        <v>638</v>
+        <v>4837</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152902</t>
+          <t xml:space="preserve">311151610</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F105">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F106">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F107">
@@ -5381,25 +5381,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4327342</t>
+          <t xml:space="preserve">8850144</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F108">
-        <v>2984</v>
+        <v>638</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311153978</t>
+          <t xml:space="preserve">311152902</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-15</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5431,35 +5431,35 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804662</t>
+          <t xml:space="preserve">4327342</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F109">
-        <v>252</v>
+        <v>2984</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199864</t>
+          <t xml:space="preserve">311153978</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-01-15</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339928</t>
+          <t xml:space="preserve">4301650</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5490,26 +5490,26 @@
         </is>
       </c>
       <c r="F110">
-        <v>530</v>
+        <v>1231</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199872</t>
+          <t xml:space="preserve">311183741</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5531,35 +5531,35 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">7904367</t>
+          <t xml:space="preserve">4301650</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F111">
-        <v>636</v>
+        <v>1139</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199858</t>
+          <t xml:space="preserve">311183741</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9887423</t>
+          <t xml:space="preserve">4339928</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5590,11 +5590,11 @@
         </is>
       </c>
       <c r="F112">
-        <v>860</v>
+        <v>530</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199868</t>
+          <t xml:space="preserve">311199872</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8154869</t>
+          <t xml:space="preserve">7904367</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5640,16 +5640,16 @@
         </is>
       </c>
       <c r="F113">
-        <v>987</v>
+        <v>636</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200257</t>
+          <t xml:space="preserve">311199858</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840495</t>
+          <t xml:space="preserve">9887423</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="F114">
-        <v>274</v>
+        <v>860</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202904</t>
+          <t xml:space="preserve">311199868</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293955, 100910530</t>
+          <t xml:space="preserve">8154869</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5740,16 +5740,16 @@
         </is>
       </c>
       <c r="F115">
-        <v>254</v>
+        <v>987</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207192</t>
+          <t xml:space="preserve">311200257</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647417</t>
+          <t xml:space="preserve">7840495</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="F116">
-        <v>1192</v>
+        <v>274</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207214</t>
+          <t xml:space="preserve">311202904</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5831,20 +5831,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647417</t>
+          <t xml:space="preserve">4293955, 100910530</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F117">
-        <v>509</v>
+        <v>254</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207214</t>
+          <t xml:space="preserve">311207192</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5886,15 +5886,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F118">
-        <v>1021</v>
+        <v>1192</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207203</t>
+          <t xml:space="preserve">311207214</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5931,20 +5931,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9818698</t>
+          <t xml:space="preserve">5647417</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F119">
-        <v>1300</v>
+        <v>509</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207188</t>
+          <t xml:space="preserve">311207214</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5981,25 +5981,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295853</t>
+          <t xml:space="preserve">5647417</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F120">
-        <v>2424</v>
+        <v>1021</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207752</t>
+          <t xml:space="preserve">311207203</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314102</t>
+          <t xml:space="preserve">9818698</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6040,16 +6040,16 @@
         </is>
       </c>
       <c r="F121">
-        <v>1055</v>
+        <v>1300</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207747</t>
+          <t xml:space="preserve">311207188</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6081,25 +6081,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">10130516</t>
+          <t xml:space="preserve">4295853</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F122">
-        <v>3110</v>
+        <v>2424</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207985</t>
+          <t xml:space="preserve">311207752</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295853</t>
+          <t xml:space="preserve">8314102</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6140,16 +6140,16 @@
         </is>
       </c>
       <c r="F123">
-        <v>1226</v>
+        <v>1055</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207923</t>
+          <t xml:space="preserve">311207747</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640267</t>
+          <t xml:space="preserve">10130516</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -6190,16 +6190,16 @@
         </is>
       </c>
       <c r="F124">
-        <v>438</v>
+        <v>3110</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208851</t>
+          <t xml:space="preserve">311207985</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-27</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">333777, 333778</t>
+          <t xml:space="preserve">4295853</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -6240,16 +6240,16 @@
         </is>
       </c>
       <c r="F125">
-        <v>2559</v>
+        <v>1226</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209730</t>
+          <t xml:space="preserve">311207923</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">4327537</t>
+          <t xml:space="preserve">5640267</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F126">
-        <v>346</v>
+        <v>438</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209480</t>
+          <t xml:space="preserve">311208851</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">323774, 323775, 323776</t>
+          <t xml:space="preserve">8831643</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -6690,16 +6690,16 @@
         </is>
       </c>
       <c r="F134">
-        <v>1533</v>
+        <v>6540</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311225557</t>
+          <t xml:space="preserve">311227853</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-31</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831643</t>
+          <t xml:space="preserve">9722201, 100756152</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6740,11 +6740,11 @@
         </is>
       </c>
       <c r="F135">
-        <v>6540</v>
+        <v>1521</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227853</t>
+          <t xml:space="preserve">311227856</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722201, 100756152</t>
+          <t xml:space="preserve">7735835</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -6790,16 +6790,16 @@
         </is>
       </c>
       <c r="F136">
-        <v>1521</v>
+        <v>1889</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227856</t>
+          <t xml:space="preserve">311229887</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">7735835</t>
+          <t xml:space="preserve">4292375</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -6840,16 +6840,16 @@
         </is>
       </c>
       <c r="F137">
-        <v>1889</v>
+        <v>5680</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229887</t>
+          <t xml:space="preserve">311230499</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6886,15 +6886,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F138">
-        <v>5680</v>
+        <v>4209</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230505</t>
+          <t xml:space="preserve">311230499</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4292375</t>
+          <t xml:space="preserve">8831556</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F139">
-        <v>4209</v>
+        <v>3990</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230504</t>
+          <t xml:space="preserve">311234877</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831556</t>
+          <t xml:space="preserve">5637742</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -6990,16 +6990,16 @@
         </is>
       </c>
       <c r="F140">
-        <v>3990</v>
+        <v>10292</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234877</t>
+          <t xml:space="preserve">311254786</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">5637742</t>
+          <t xml:space="preserve">9980142</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F141">
-        <v>10292</v>
+        <v>372</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254786</t>
+          <t xml:space="preserve">311290215</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7081,25 +7081,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980142</t>
+          <t xml:space="preserve">10227122</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="F142">
-        <v>372</v>
+        <v>311</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290215</t>
+          <t xml:space="preserve">311360509</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2029-02-20</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">10227122</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -7140,16 +7140,16 @@
         </is>
       </c>
       <c r="F143">
-        <v>311</v>
+        <v>3034</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360509</t>
+          <t xml:space="preserve">311438459</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-20</t>
+          <t xml:space="preserve">2030-05-18</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">1804662</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="F144">
-        <v>3034</v>
+        <v>252</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438459</t>
+          <t xml:space="preserve">311458382</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-18</t>
+          <t xml:space="preserve">2030-09-02</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100280264, 100280269, 100280265, 100280266, 100280268</t>
+          <t xml:space="preserve">100302991</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7340,16 +7340,16 @@
         </is>
       </c>
       <c r="F147">
-        <v>36105</v>
+        <v>1497</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311538497</t>
+          <t xml:space="preserve">311564096</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-31</t>
+          <t xml:space="preserve">2031-11-25</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7381,25 +7381,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">100302991</t>
+          <t xml:space="preserve">5646875</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F148">
-        <v>1497</v>
+        <v>1251</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564096</t>
+          <t xml:space="preserve">311568983</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-25</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7481,25 +7481,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">408943, 408944</t>
+          <t xml:space="preserve">100260046</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F150">
-        <v>11768</v>
+        <v>2044</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311581729</t>
+          <t xml:space="preserve">311592787</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-01</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7531,25 +7531,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">100260046</t>
+          <t xml:space="preserve">5646174</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F151">
-        <v>2044</v>
+        <v>430</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592787</t>
+          <t xml:space="preserve">311618333</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-08-03</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7581,25 +7581,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">322540, 322541</t>
+          <t xml:space="preserve">8263816</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F152">
-        <v>9459</v>
+        <v>324</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594650</t>
+          <t xml:space="preserve">311664771</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-22</t>
+          <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646174</t>
+          <t xml:space="preserve">1463870</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -7640,16 +7640,16 @@
         </is>
       </c>
       <c r="F153">
-        <v>430</v>
+        <v>1771</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618333</t>
+          <t xml:space="preserve">311725662</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-03</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7681,25 +7681,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t xml:space="preserve">331936, 331937</t>
+          <t xml:space="preserve">1463870</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F154">
-        <v>6602</v>
+        <v>1786</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644337</t>
+          <t xml:space="preserve">311725662</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-23</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7731,25 +7731,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t xml:space="preserve">332890, 332891</t>
+          <t xml:space="preserve">1463870</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F155">
-        <v>3476</v>
+        <v>464</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311645249</t>
+          <t xml:space="preserve">311725662</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-27</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7781,25 +7781,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8263816</t>
+          <t xml:space="preserve">1463870</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F156">
-        <v>324</v>
+        <v>2820</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664771</t>
+          <t xml:space="preserve">311725662</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-07</t>
+          <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7836,11 +7836,11 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F157">
-        <v>1771</v>
+        <v>422</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -7886,11 +7886,11 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F158">
-        <v>1786</v>
+        <v>1190</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -7931,20 +7931,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463870</t>
+          <t xml:space="preserve">4339462</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F159">
-        <v>464</v>
+        <v>356</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725662</t>
+          <t xml:space="preserve">311725660</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463870</t>
+          <t xml:space="preserve">5640943</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F160">
-        <v>2820</v>
+        <v>502</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725662</t>
+          <t xml:space="preserve">311736798</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -8031,25 +8031,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463870</t>
+          <t xml:space="preserve">4301565</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F161">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725662</t>
+          <t xml:space="preserve">311738627</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8081,25 +8081,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463870</t>
+          <t xml:space="preserve">5640942</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F162">
-        <v>1190</v>
+        <v>502</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725662</t>
+          <t xml:space="preserve">311738631</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339462</t>
+          <t xml:space="preserve">5642100</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -8140,16 +8140,16 @@
         </is>
       </c>
       <c r="F163">
-        <v>356</v>
+        <v>1847</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311725660</t>
+          <t xml:space="preserve">311738637</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-29</t>
+          <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640943</t>
+          <t xml:space="preserve">7960151</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -8190,16 +8190,16 @@
         </is>
       </c>
       <c r="F164">
-        <v>502</v>
+        <v>973</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311736798</t>
+          <t xml:space="preserve">311738816</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-02</t>
+          <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8231,25 +8231,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301565</t>
+          <t xml:space="preserve">4337162</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F165">
-        <v>442</v>
+        <v>1618</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738627</t>
+          <t xml:space="preserve">311739167</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-13</t>
+          <t xml:space="preserve">2034-02-15</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640942</t>
+          <t xml:space="preserve">100035977</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="F166">
-        <v>502</v>
+        <v>900</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738631</t>
+          <t xml:space="preserve">311739352</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-13</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642100</t>
+          <t xml:space="preserve">5643101</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8340,16 +8340,16 @@
         </is>
       </c>
       <c r="F167">
-        <v>1847</v>
+        <v>1549</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738637</t>
+          <t xml:space="preserve">311739345</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-13</t>
+          <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">7960151</t>
+          <t xml:space="preserve">10167488</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8390,16 +8390,16 @@
         </is>
       </c>
       <c r="F168">
-        <v>973</v>
+        <v>1252</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738816</t>
+          <t xml:space="preserve">311740291</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-14</t>
+          <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8431,25 +8431,25 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">4337162</t>
+          <t xml:space="preserve">4287792</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F169">
-        <v>1618</v>
+        <v>1640</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739167</t>
+          <t xml:space="preserve">311740716</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-15</t>
+          <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035977</t>
+          <t xml:space="preserve">4292353</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8490,16 +8490,16 @@
         </is>
       </c>
       <c r="F170">
-        <v>900</v>
+        <v>437</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739352</t>
+          <t xml:space="preserve">311740714</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5643101</t>
+          <t xml:space="preserve">100042652</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8540,16 +8540,16 @@
         </is>
       </c>
       <c r="F171">
-        <v>1549</v>
+        <v>1595</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739345</t>
+          <t xml:space="preserve">311742330</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-16</t>
+          <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t xml:space="preserve">10167488</t>
+          <t xml:space="preserve">5645217</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -8590,16 +8590,16 @@
         </is>
       </c>
       <c r="F172">
-        <v>1252</v>
+        <v>1065</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740291</t>
+          <t xml:space="preserve">311743202</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-21</t>
+          <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8631,25 +8631,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287792</t>
+          <t xml:space="preserve">5645217</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F173">
-        <v>1640</v>
+        <v>720</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740716</t>
+          <t xml:space="preserve">311743202</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-23</t>
+          <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4292353</t>
+          <t xml:space="preserve">100565240</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -8690,16 +8690,16 @@
         </is>
       </c>
       <c r="F174">
-        <v>437</v>
+        <v>1477</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311740714</t>
+          <t xml:space="preserve">311752411</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-23</t>
+          <t xml:space="preserve">2034-04-16</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">100042652</t>
+          <t xml:space="preserve">4340275</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -8740,16 +8740,16 @@
         </is>
       </c>
       <c r="F175">
-        <v>1595</v>
+        <v>5113</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311742330</t>
+          <t xml:space="preserve">311771128</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-01</t>
+          <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8781,25 +8781,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5645217</t>
+          <t xml:space="preserve">4340275</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F176">
-        <v>1065</v>
+        <v>3965</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743202</t>
+          <t xml:space="preserve">311771127</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-06</t>
+          <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8831,25 +8831,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5645217</t>
+          <t xml:space="preserve">4340275</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F177">
-        <v>720</v>
+        <v>3096</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311743202</t>
+          <t xml:space="preserve">311771123</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-06</t>
+          <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8881,25 +8881,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t xml:space="preserve">100565240</t>
+          <t xml:space="preserve">4340275</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F178">
-        <v>1477</v>
+        <v>2623</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311752411</t>
+          <t xml:space="preserve">311771126</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-16</t>
+          <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340275</t>
+          <t xml:space="preserve">4340323</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -8940,16 +8940,16 @@
         </is>
       </c>
       <c r="F179">
-        <v>5113</v>
+        <v>425</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771128</t>
+          <t xml:space="preserve">311800640</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-03</t>
+          <t xml:space="preserve">2034-12-03</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340275</t>
+          <t xml:space="preserve">10098286</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F180">
-        <v>3965</v>
+        <v>603</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771127</t>
+          <t xml:space="preserve">311801295</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-03</t>
+          <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9031,25 +9031,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340275</t>
+          <t xml:space="preserve">4287611</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F181">
-        <v>3096</v>
+        <v>554</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771123</t>
+          <t xml:space="preserve">311801299</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-03</t>
+          <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9081,25 +9081,25 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340275</t>
+          <t xml:space="preserve">4293715</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F182">
-        <v>2623</v>
+        <v>596</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771126</t>
+          <t xml:space="preserve">311801280</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-03</t>
+          <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340323</t>
+          <t xml:space="preserve">4297823</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -9140,16 +9140,16 @@
         </is>
       </c>
       <c r="F183">
-        <v>425</v>
+        <v>560</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311800640</t>
+          <t xml:space="preserve">311801290</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-03</t>
+          <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098286</t>
+          <t xml:space="preserve">7938207</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -9190,11 +9190,11 @@
         </is>
       </c>
       <c r="F184">
-        <v>603</v>
+        <v>540</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801295</t>
+          <t xml:space="preserve">311801310</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287611</t>
+          <t xml:space="preserve">8190251</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -9240,11 +9240,11 @@
         </is>
       </c>
       <c r="F185">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801299</t>
+          <t xml:space="preserve">311801284</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293715</t>
+          <t xml:space="preserve">4268440</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -9290,16 +9290,16 @@
         </is>
       </c>
       <c r="F186">
-        <v>596</v>
+        <v>5883</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801280</t>
+          <t xml:space="preserve">311801400</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-05</t>
+          <t xml:space="preserve">2034-12-06</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9331,25 +9331,25 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">4297823</t>
+          <t xml:space="preserve">4268440</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F187">
-        <v>560</v>
+        <v>1364</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801290</t>
+          <t xml:space="preserve">311801400</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-05</t>
+          <t xml:space="preserve">2034-12-06</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938207</t>
+          <t xml:space="preserve">4268451</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -9390,16 +9390,16 @@
         </is>
       </c>
       <c r="F188">
-        <v>540</v>
+        <v>2326</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801310</t>
+          <t xml:space="preserve">311801399</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-05</t>
+          <t xml:space="preserve">2034-12-06</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">8190251</t>
+          <t xml:space="preserve">4340325</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9440,16 +9440,16 @@
         </is>
       </c>
       <c r="F189">
-        <v>537</v>
+        <v>1126</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801284</t>
+          <t xml:space="preserve">311801874</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-05</t>
+          <t xml:space="preserve">2034-12-10</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268440</t>
+          <t xml:space="preserve">4340325</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F190">
-        <v>5883</v>
+        <v>277</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801400</t>
+          <t xml:space="preserve">311801874</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-06</t>
+          <t xml:space="preserve">2034-12-10</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9531,25 +9531,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268440</t>
+          <t xml:space="preserve">5642536</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F191">
-        <v>1364</v>
+        <v>1306</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801400</t>
+          <t xml:space="preserve">311803062</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-06</t>
+          <t xml:space="preserve">2034-12-17</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9581,25 +9581,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268451</t>
+          <t xml:space="preserve">5642536</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F192">
-        <v>2326</v>
+        <v>669</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801399</t>
+          <t xml:space="preserve">311803062</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-06</t>
+          <t xml:space="preserve">2034-12-17</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340325</t>
+          <t xml:space="preserve">4337484</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -9640,16 +9640,16 @@
         </is>
       </c>
       <c r="F193">
-        <v>1126</v>
+        <v>1430</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801874</t>
+          <t xml:space="preserve">311803455</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-10</t>
+          <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340325</t>
+          <t xml:space="preserve">4337484</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9690,16 +9690,16 @@
         </is>
       </c>
       <c r="F194">
-        <v>277</v>
+        <v>494</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801874</t>
+          <t xml:space="preserve">311803455</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-10</t>
+          <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9731,25 +9731,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642536</t>
+          <t xml:space="preserve">100548298</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F195">
-        <v>1306</v>
+        <v>1331</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803062</t>
+          <t xml:space="preserve">311808529</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-17</t>
+          <t xml:space="preserve">2035-01-29</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9781,25 +9781,25 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642536</t>
+          <t xml:space="preserve">4293329</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F196">
-        <v>669</v>
+        <v>3090</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803062</t>
+          <t xml:space="preserve">311810420</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-17</t>
+          <t xml:space="preserve">2035-02-07</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9831,7 +9831,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4337484</t>
+          <t xml:space="preserve">5638632</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9840,16 +9840,16 @@
         </is>
       </c>
       <c r="F197">
-        <v>1430</v>
+        <v>2420</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803455</t>
+          <t xml:space="preserve">311811436</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-18</t>
+          <t xml:space="preserve">2035-02-13</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4337484</t>
+          <t xml:space="preserve">5638632</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -9890,16 +9890,16 @@
         </is>
       </c>
       <c r="F198">
-        <v>494</v>
+        <v>395</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803455</t>
+          <t xml:space="preserve">311811436</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-18</t>
+          <t xml:space="preserve">2035-02-13</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9931,25 +9931,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t xml:space="preserve">100548298</t>
+          <t xml:space="preserve">1804662</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F199">
-        <v>1331</v>
+        <v>3947</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311808529</t>
+          <t xml:space="preserve">311819120</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-29</t>
+          <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9981,25 +9981,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293329</t>
+          <t xml:space="preserve">1804662</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="F200">
-        <v>3090</v>
+        <v>1452</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311810420</t>
+          <t xml:space="preserve">311819120</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-07</t>
+          <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -10031,25 +10031,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5638632</t>
+          <t xml:space="preserve">1804662</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F201">
-        <v>2420</v>
+        <v>968</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311811436</t>
+          <t xml:space="preserve">311819120</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-13</t>
+          <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -10081,25 +10081,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5638632</t>
+          <t xml:space="preserve">1804662</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F202">
-        <v>395</v>
+        <v>1204</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311811436</t>
+          <t xml:space="preserve">311819120</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-13</t>
+          <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -10136,11 +10136,11 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F203">
-        <v>3947</v>
+        <v>1386</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -10181,25 +10181,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804662</t>
+          <t xml:space="preserve">4293742</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F204">
-        <v>1452</v>
+        <v>2818</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819120</t>
+          <t xml:space="preserve">311819601</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-20</t>
+          <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804662</t>
+          <t xml:space="preserve">4293742</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -10240,16 +10240,16 @@
         </is>
       </c>
       <c r="F205">
-        <v>968</v>
+        <v>1291</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819120</t>
+          <t xml:space="preserve">311819601</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-20</t>
+          <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804662</t>
+          <t xml:space="preserve">4293742</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -10290,16 +10290,16 @@
         </is>
       </c>
       <c r="F206">
-        <v>1204</v>
+        <v>2277</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819120</t>
+          <t xml:space="preserve">311819601</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-20</t>
+          <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804662</t>
+          <t xml:space="preserve">4293742</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -10340,16 +10340,16 @@
         </is>
       </c>
       <c r="F207">
-        <v>1386</v>
+        <v>1699</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819120</t>
+          <t xml:space="preserve">311819601</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-20</t>
+          <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10386,11 +10386,11 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F208">
-        <v>2818</v>
+        <v>304</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F209">
@@ -10481,20 +10481,20 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293742</t>
+          <t xml:space="preserve">5640268</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F210">
-        <v>2277</v>
+        <v>2396</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819601</t>
+          <t xml:space="preserve">311819603</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -10531,20 +10531,20 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293742</t>
+          <t xml:space="preserve">5640268</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F211">
-        <v>1699</v>
+        <v>285</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819601</t>
+          <t xml:space="preserve">311819603</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -10581,20 +10581,20 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293742</t>
+          <t xml:space="preserve">5640268</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F212">
-        <v>304</v>
+        <v>884</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819601</t>
+          <t xml:space="preserve">311819603</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -10631,20 +10631,20 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293742</t>
+          <t xml:space="preserve">5640268</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F213">
-        <v>1291</v>
+        <v>670</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819601</t>
+          <t xml:space="preserve">311819603</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640268</t>
+          <t xml:space="preserve">4327537</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -10690,16 +10690,16 @@
         </is>
       </c>
       <c r="F214">
-        <v>2396</v>
+        <v>3070</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819603</t>
+          <t xml:space="preserve">311820706</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-24</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10731,25 +10731,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640268</t>
+          <t xml:space="preserve">4327537</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F215">
-        <v>285</v>
+        <v>346</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819603</t>
+          <t xml:space="preserve">311820707</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-24</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10781,25 +10781,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640268</t>
+          <t xml:space="preserve">4327537</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="F216">
-        <v>884</v>
+        <v>1479</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819603</t>
+          <t xml:space="preserve">311820707</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-24</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10831,25 +10831,25 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640268</t>
+          <t xml:space="preserve">4327537</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F217">
-        <v>670</v>
+        <v>1266</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311819603</t>
+          <t xml:space="preserve">311820707</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-24</t>
+          <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4327537</t>
+          <t xml:space="preserve">4334957</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10890,11 +10890,11 @@
         </is>
       </c>
       <c r="F218">
-        <v>3070</v>
+        <v>3136</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820706</t>
+          <t xml:space="preserve">311820714</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -10931,20 +10931,20 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4327537</t>
+          <t xml:space="preserve">4334957</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="F219">
-        <v>1479</v>
+        <v>277</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820712</t>
+          <t xml:space="preserve">311820714</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -10986,15 +10986,15 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F220">
-        <v>3136</v>
+        <v>412</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820714</t>
+          <t xml:space="preserve">311820930</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -11036,11 +11036,11 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F221">
-        <v>277</v>
+        <v>2123</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -11086,15 +11086,15 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F222">
-        <v>412</v>
+        <v>960</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820930</t>
+          <t xml:space="preserve">311820714</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -11136,11 +11136,11 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F223">
-        <v>2123</v>
+        <v>786</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -11186,11 +11186,11 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="F224">
-        <v>960</v>
+        <v>709</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -11236,11 +11236,11 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="F225">
-        <v>786</v>
+        <v>418</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -11286,11 +11286,11 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="F226">
-        <v>709</v>
+        <v>315</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -11331,20 +11331,20 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">4334957</t>
+          <t xml:space="preserve">8831588</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F227">
-        <v>418</v>
+        <v>1607</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820714</t>
+          <t xml:space="preserve">311820726</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -11381,20 +11381,20 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4334957</t>
+          <t xml:space="preserve">8831588</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="F228">
-        <v>315</v>
+        <v>2503</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820714</t>
+          <t xml:space="preserve">311820726</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -11436,11 +11436,11 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="F229">
-        <v>1607</v>
+        <v>1756</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -11486,11 +11486,11 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="F230">
-        <v>2503</v>
+        <v>1511</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -11531,25 +11531,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831588</t>
+          <t xml:space="preserve">4301495</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="F231">
-        <v>1756</v>
+        <v>515</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820726</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-27</t>
+          <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11581,25 +11581,25 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831588</t>
+          <t xml:space="preserve">4301495</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="F232">
-        <v>1511</v>
+        <v>2844</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820726</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-27</t>
+          <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11636,15 +11636,15 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="F233">
-        <v>515</v>
+        <v>2848</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -11686,15 +11686,15 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="F234">
-        <v>2848</v>
+        <v>298</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -11794,7 +11794,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821144</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823878</t>
+          <t xml:space="preserve">311823877</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">

--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -91,7 +91,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chr M Østergaards Vej 4</t>
+          <t xml:space="preserve">Brådhusvej 34</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -101,7 +101,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100280264, 100280269, 100280265, 100280266, 100280268</t>
+          <t xml:space="preserve">4293717</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -110,7 +110,7 @@
         </is>
       </c>
       <c r="H2">
-        <v>36105</v>
+        <v>502</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -151,7 +151,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangsalle 57</t>
+          <t xml:space="preserve">Carolinelundsvej 2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -161,16 +161,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100548298</t>
+          <t xml:space="preserve">5646746</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H3">
-        <v>450</v>
+        <v>2801</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -211,7 +211,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenkrantzvej 32</t>
+          <t xml:space="preserve">Carolinelundsvej 2C</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -221,16 +221,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463273</t>
+          <t xml:space="preserve">738514, 5646746</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H4">
-        <v>450</v>
+        <v>255</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -271,7 +271,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endelavevej 14C</t>
+          <t xml:space="preserve">Egevej 5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -281,16 +281,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">321593, 321594, 321595</t>
+          <t xml:space="preserve">4287946</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H5">
-        <v>3496</v>
+        <v>1235</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -331,7 +331,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørretorv 1E</t>
+          <t xml:space="preserve">Endelavevej 14C</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -341,16 +341,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">322540, 322541</t>
+          <t xml:space="preserve">321593, 321594, 321595</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H6">
-        <v>9459</v>
+        <v>3496</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -391,26 +391,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parallelvej 6A</t>
+          <t xml:space="preserve">Endelavevej 5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">8751</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">323774, 323775, 323776</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H7">
-        <v>1533</v>
+        <v>591</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -451,7 +451,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 1</t>
+          <t xml:space="preserve">Endelavevej 5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -461,16 +461,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">324132, 324133</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H8">
-        <v>1473</v>
+        <v>517</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -511,7 +511,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegade 23</t>
+          <t xml:space="preserve">Endelavevej 5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -521,16 +521,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">325727, 325728</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H9">
-        <v>2343</v>
+        <v>1811</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegade 23</t>
+          <t xml:space="preserve">Endelavevej 5A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -581,16 +581,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">325727, 325728</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H10">
-        <v>352</v>
+        <v>539</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegade 23</t>
+          <t xml:space="preserve">Fuglevangsvej 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -641,16 +641,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">325727, 325728</t>
+          <t xml:space="preserve">5647421</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H11">
-        <v>352</v>
+        <v>276</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 66A</t>
+          <t xml:space="preserve">Gl Sognevej 8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -701,16 +701,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">331936, 331937</t>
+          <t xml:space="preserve">7084738</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H12">
-        <v>6602</v>
+        <v>273</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silkeborgvej 245B</t>
+          <t xml:space="preserve">Højvangsalle 57</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -761,16 +761,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">332890, 332891</t>
+          <t xml:space="preserve">100548298</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H13">
-        <v>3476</v>
+        <v>450</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -811,17 +811,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Vissingvej 26B</t>
+          <t xml:space="preserve">Kongevejen 26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8789</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">333777, 333778</t>
+          <t xml:space="preserve">4298855</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="H14">
-        <v>2559</v>
+        <v>450</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -871,26 +871,26 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebakken 1</t>
+          <t xml:space="preserve">Kongevejen 30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8789</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">408943, 408944</t>
+          <t xml:space="preserve">4298855</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H15">
-        <v>11768</v>
+        <v>407</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -931,26 +931,26 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Kraghsvej 3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268440</t>
+          <t xml:space="preserve">738303, 5644002</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H16">
-        <v>458</v>
+        <v>1039</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -991,17 +991,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 5</t>
+          <t xml:space="preserve">Krudthusvej 16</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8660</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4273040</t>
+          <t xml:space="preserve">738401, 5646176</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="H17">
-        <v>455</v>
+        <v>394</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevej 5</t>
+          <t xml:space="preserve">Langelinie 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1061,16 +1061,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287946</t>
+          <t xml:space="preserve">9031557</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H18">
-        <v>1235</v>
+        <v>853</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brådhusvej 34</t>
+          <t xml:space="preserve">Langmarksvej 45</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293717</t>
+          <t xml:space="preserve">738445, 9962230</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="H19">
-        <v>502</v>
+        <v>1206</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1171,26 +1171,26 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 26</t>
+          <t xml:space="preserve">Langmarksvej 47</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">8789</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298855</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H20">
-        <v>450</v>
+        <v>2345</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1231,26 +1231,26 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 30</t>
+          <t xml:space="preserve">Langmarksvej 53</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8789</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298855</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H21">
-        <v>407</v>
+        <v>2962</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognegårdsvej 4</t>
+          <t xml:space="preserve">Langmarksvej 86</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1301,16 +1301,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">4337482</t>
+          <t xml:space="preserve">5642082</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H22">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordrevej 16</t>
+          <t xml:space="preserve">Lindvigsvej 4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1361,16 +1361,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339928</t>
+          <t xml:space="preserve">8831643</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H23">
-        <v>524</v>
+        <v>1841</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Holms Vej 4</t>
+          <t xml:space="preserve">Nordrevej 16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1421,16 +1421,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5637741</t>
+          <t xml:space="preserve">4339928</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H24">
-        <v>998</v>
+        <v>524</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langmarksvej 86</t>
+          <t xml:space="preserve">Robert Holms Vej 4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1541,16 +1541,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642082</t>
+          <t xml:space="preserve">5637741</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H26">
-        <v>335</v>
+        <v>998</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langmarksvej 47</t>
+          <t xml:space="preserve">Rosenkrantzvej 32</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1601,16 +1601,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">1463273</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H27">
-        <v>2345</v>
+        <v>450</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langmarksvej 53</t>
+          <t xml:space="preserve">Schüttesvej 15</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1661,16 +1661,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">8831521</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H28">
-        <v>2962</v>
+        <v>1452</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolinelundsvej 2</t>
+          <t xml:space="preserve">Schüttesvej 17</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1721,16 +1721,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646746</t>
+          <t xml:space="preserve">8831521</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H29">
-        <v>2801</v>
+        <v>705</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sundvej 1A</t>
+          <t xml:space="preserve">Schüttesvej 19</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1781,16 +1781,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646746</t>
+          <t xml:space="preserve">8831521</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H30">
-        <v>1051</v>
+        <v>1098</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endelavevej 5A</t>
+          <t xml:space="preserve">Silkeborgvej 44</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1841,16 +1841,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">738358, 8843882</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H31">
-        <v>539</v>
+        <v>1240</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endelavevej 5</t>
+          <t xml:space="preserve">Silkeborgvej 44</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1901,16 +1901,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">738358, 8843882</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H32">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1951,26 +1951,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endelavevej 5</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">4268440</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H33">
-        <v>517</v>
+        <v>458</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2011,17 +2011,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endelavevej 5</t>
+          <t xml:space="preserve">Skovvejen 26</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">738434, 4268923</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="H34">
-        <v>1811</v>
+        <v>460</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 1</t>
+          <t xml:space="preserve">Sognegårdsvej 4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2081,16 +2081,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647421</t>
+          <t xml:space="preserve">4337482</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H35">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Sognevej 8</t>
+          <t xml:space="preserve">Sognegårdsvej 4</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2141,16 +2141,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">7084738</t>
+          <t xml:space="preserve">738317, 4337482</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H36">
-        <v>273</v>
+        <v>816</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kraghsvej 3</t>
+          <t xml:space="preserve">Sundvej 1A</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2201,16 +2201,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">738303, 5644002</t>
+          <t xml:space="preserve">5646746</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H37">
-        <v>1039</v>
+        <v>1051</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognegårdsvej 4</t>
+          <t xml:space="preserve">Søvej 1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">738317, 4337482</t>
+          <t xml:space="preserve">8831513</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="H38">
-        <v>816</v>
+        <v>550</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silkeborgvej 44</t>
+          <t xml:space="preserve">Ternevej 83</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2321,16 +2321,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">738358, 8843882</t>
+          <t xml:space="preserve">738371, 4339668</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H39">
-        <v>1240</v>
+        <v>1200</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2371,26 +2371,26 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silkeborgvej 44</t>
+          <t xml:space="preserve">Ådalen 5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8660</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">738358, 8843882</t>
+          <t xml:space="preserve">4273040</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H40">
-        <v>602</v>
+        <v>455</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ternevej 83</t>
+          <t xml:space="preserve">Silkeborgvej 177</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">738371, 4339668</t>
+          <t xml:space="preserve">4301565</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H41">
-        <v>1200</v>
+        <v>458</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200004055</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2017-12-18</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krudthusvej 16</t>
+          <t xml:space="preserve">Rådvedvej 5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">738401, 5646176</t>
+          <t xml:space="preserve">4287793</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2510,21 +2510,21 @@
         </is>
       </c>
       <c r="H42">
-        <v>394</v>
+        <v>311</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200005814</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-04-29</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2551,40 +2551,40 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvejen 26</t>
+          <t xml:space="preserve">Vestergade 7B</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">738434, 4268923</t>
+          <t xml:space="preserve">9683312</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H43">
-        <v>460</v>
+        <v>1262</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200006369</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-06-16</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langmarksvej 45</t>
+          <t xml:space="preserve">Langmarksvej 53</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">738445, 9962230</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H44">
-        <v>1206</v>
+        <v>1920</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200007213</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2018-08-19</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolinelundsvej 2C</t>
+          <t xml:space="preserve">Hattingvej 14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2681,30 +2681,30 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">738514, 5646746</t>
+          <t xml:space="preserve">738335, 4327352</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H45">
-        <v>255</v>
+        <v>715</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200014768</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-06-10</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvej 1</t>
+          <t xml:space="preserve">Stationsvej 3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831513</t>
+          <t xml:space="preserve">4296269</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="H46">
-        <v>550</v>
+        <v>744</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200019232</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schüttesvej 17</t>
+          <t xml:space="preserve">Endelavevej 5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831521</t>
+          <t xml:space="preserve">5646870</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H47">
-        <v>705</v>
+        <v>1378</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200025850</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-18</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -2851,40 +2851,40 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schüttesvej 19</t>
+          <t xml:space="preserve">Storegade 51</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8752</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831521</t>
+          <t xml:space="preserve">100020899</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H48">
-        <v>1098</v>
+        <v>1296</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200032357</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-08</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schüttesvej 15</t>
+          <t xml:space="preserve">Hybenvej 12</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2921,30 +2921,30 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831521</t>
+          <t xml:space="preserve">5642094</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H49">
-        <v>1452</v>
+        <v>701</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200032602</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2020-06-15</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindvigsvej 4</t>
+          <t xml:space="preserve">Egevej 5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831643</t>
+          <t xml:space="preserve">4287946</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H50">
-        <v>1841</v>
+        <v>2266</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200047462</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-03-31</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langelinie 2</t>
+          <t xml:space="preserve">Lovbyvej 79</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3041,30 +3041,30 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">9031557</t>
+          <t xml:space="preserve">7895719</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H51">
-        <v>853</v>
+        <v>273</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100217499</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2021-04-14</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silkeborgvej 177</t>
+          <t xml:space="preserve">Højvangsalle 20</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3101,25 +3101,25 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301565</t>
+          <t xml:space="preserve">1463870</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H52">
-        <v>458</v>
+        <v>3185</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">200004055</t>
+          <t xml:space="preserve">200049551</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017-12-18</t>
+          <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3151,17 +3151,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådvedvej 5</t>
+          <t xml:space="preserve">Kirkevej 5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8751</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287793</t>
+          <t xml:space="preserve">8742377</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3170,16 +3170,16 @@
         </is>
       </c>
       <c r="H53">
-        <v>311</v>
+        <v>3617</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">200005814</t>
+          <t xml:space="preserve">200050729</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-04-29</t>
+          <t xml:space="preserve">2021-06-28</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 7B</t>
+          <t xml:space="preserve">Smedebakken 1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9683312</t>
+          <t xml:space="preserve">324132, 324133</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3230,16 +3230,16 @@
         </is>
       </c>
       <c r="H54">
-        <v>1262</v>
+        <v>1473</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">200006369</t>
+          <t xml:space="preserve">200052534</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-06-16</t>
+          <t xml:space="preserve">2021-09-01</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3271,35 +3271,35 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langmarksvej 53</t>
+          <t xml:space="preserve">Søndergade 41</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">7750871</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H55">
-        <v>1920</v>
+        <v>1254</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200007213</t>
+          <t xml:space="preserve">200053158</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-08-19</t>
+          <t xml:space="preserve">2021-09-22</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3331,35 +3331,35 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hattingvej 14</t>
+          <t xml:space="preserve">Søndergade 43</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">738335, 4327352</t>
+          <t xml:space="preserve">7750871</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H56">
-        <v>715</v>
+        <v>2522</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014768</t>
+          <t xml:space="preserve">200053159</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-10</t>
+          <t xml:space="preserve">2021-09-22</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 3</t>
+          <t xml:space="preserve">Kildegade 23</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4296269</t>
+          <t xml:space="preserve">325727, 325728</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3410,16 +3410,16 @@
         </is>
       </c>
       <c r="H57">
-        <v>744</v>
+        <v>2343</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019232</t>
+          <t xml:space="preserve">200053294</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-25</t>
+          <t xml:space="preserve">2021-09-27</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endelavevej 5</t>
+          <t xml:space="preserve">Kildegade 23</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3461,25 +3461,25 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646870</t>
+          <t xml:space="preserve">325727, 325728</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H58">
-        <v>1378</v>
+        <v>352</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025850</t>
+          <t xml:space="preserve">200053294</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-18</t>
+          <t xml:space="preserve">2021-09-27</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -3511,35 +3511,35 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 51</t>
+          <t xml:space="preserve">Kildegade 23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">100020899</t>
+          <t xml:space="preserve">325727, 325728</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H59">
-        <v>1296</v>
+        <v>352</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032357</t>
+          <t xml:space="preserve">200053294</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-08</t>
+          <t xml:space="preserve">2021-09-27</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvej 12</t>
+          <t xml:space="preserve">Madevej 2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642094</t>
+          <t xml:space="preserve">5646862</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="H60">
-        <v>701</v>
+        <v>1169</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032602</t>
+          <t xml:space="preserve">200053806</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-15</t>
+          <t xml:space="preserve">2021-10-12</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -3631,35 +3631,35 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egevej 5</t>
+          <t xml:space="preserve">Vestbirkvej 3A</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8752</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287946</t>
+          <t xml:space="preserve">4297715</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H61">
-        <v>2266</v>
+        <v>3047</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047462</t>
+          <t xml:space="preserve">200056422</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-03-31</t>
+          <t xml:space="preserve">2022-01-03</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovbyvej 79</t>
+          <t xml:space="preserve">Nørrebrogade 38A</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3701,25 +3701,25 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">7895719</t>
+          <t xml:space="preserve">5643101</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H62">
-        <v>273</v>
+        <v>572</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">100217499</t>
+          <t xml:space="preserve">200057417</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-14</t>
+          <t xml:space="preserve">2022-02-14</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangsalle 20</t>
+          <t xml:space="preserve">Kildegade 54</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3761,25 +3761,25 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463870</t>
+          <t xml:space="preserve">8194376</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H63">
-        <v>3185</v>
+        <v>1844</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">200049551</t>
+          <t xml:space="preserve">310004216</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-05-26</t>
+          <t xml:space="preserve">2022-09-13</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 5</t>
+          <t xml:space="preserve">Skovvej 13A</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3821,25 +3821,25 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8742377</t>
+          <t xml:space="preserve">4292353</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H64">
-        <v>3617</v>
+        <v>464</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">200050729</t>
+          <t xml:space="preserve">310006732</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-06-28</t>
+          <t xml:space="preserve">2022-10-01</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -3871,35 +3871,35 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 41</t>
+          <t xml:space="preserve">Skovvej 13A</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8751</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">7750871</t>
+          <t xml:space="preserve">4292353</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H65">
-        <v>1254</v>
+        <v>261</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053158</t>
+          <t xml:space="preserve">310006732</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-22</t>
+          <t xml:space="preserve">2022-10-01</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergade 43</t>
+          <t xml:space="preserve">Møllegade 22</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3941,25 +3941,25 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">7750871</t>
+          <t xml:space="preserve">7735835</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H66">
-        <v>2522</v>
+        <v>1003</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053157</t>
+          <t xml:space="preserve">310013380</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-09-22</t>
+          <t xml:space="preserve">2022-11-14</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Madevej 2</t>
+          <t xml:space="preserve">Lovbyvej 22</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646862</t>
+          <t xml:space="preserve">5647450</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4010,16 +4010,16 @@
         </is>
       </c>
       <c r="H67">
-        <v>1169</v>
+        <v>266</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053806</t>
+          <t xml:space="preserve">310015648</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-10-12</t>
+          <t xml:space="preserve">2022-11-30</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4051,35 +4051,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestbirkvej 3A</t>
+          <t xml:space="preserve">Højen 1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4297715</t>
+          <t xml:space="preserve">4339669</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H68">
-        <v>3047</v>
+        <v>1299</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056422</t>
+          <t xml:space="preserve">310035291</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-01-03</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebrogade 38A</t>
+          <t xml:space="preserve">Højen 1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4121,25 +4121,25 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5643101</t>
+          <t xml:space="preserve">4339669</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H69">
-        <v>572</v>
+        <v>280</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200057417</t>
+          <t xml:space="preserve">310035291</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-02-14</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegade 54</t>
+          <t xml:space="preserve">Højen 1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4181,25 +4181,25 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">8194376</t>
+          <t xml:space="preserve">4339669</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H70">
-        <v>1844</v>
+        <v>1320</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">310004216</t>
+          <t xml:space="preserve">310035291</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-09-13</t>
+          <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4231,35 +4231,35 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 13A</t>
+          <t xml:space="preserve">Vesterled 1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8751</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4292353</t>
+          <t xml:space="preserve">5642531</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H71">
-        <v>464</v>
+        <v>3753</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">310006732</t>
+          <t xml:space="preserve">310037158</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-10-01</t>
+          <t xml:space="preserve">2023-04-29</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4291,35 +4291,35 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvej 13A</t>
+          <t xml:space="preserve">Skolevej 7C</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">8751</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4292353</t>
+          <t xml:space="preserve">4301856</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H72">
-        <v>261</v>
+        <v>2172</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">310006732</t>
+          <t xml:space="preserve">311053869</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-10-01</t>
+          <t xml:space="preserve">2024-05-13</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4351,35 +4351,35 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 22</t>
+          <t xml:space="preserve">Kirkevej 10B</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8751</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">7735835</t>
+          <t xml:space="preserve">100061763</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H73">
-        <v>1003</v>
+        <v>875</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">310013380</t>
+          <t xml:space="preserve">311056702</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-14</t>
+          <t xml:space="preserve">2024-05-28</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lovbyvej 22</t>
+          <t xml:space="preserve">Langmarksvej 53</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647450</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4430,16 +4430,16 @@
         </is>
       </c>
       <c r="H74">
-        <v>266</v>
+        <v>10244</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">310015648</t>
+          <t xml:space="preserve">311084316</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-11-30</t>
+          <t xml:space="preserve">2024-11-20</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højen 1</t>
+          <t xml:space="preserve">Flintebakken 145</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4481,25 +4481,25 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339669</t>
+          <t xml:space="preserve">8059978</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H75">
-        <v>1299</v>
+        <v>438</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">310035291</t>
+          <t xml:space="preserve">311109196</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-16</t>
+          <t xml:space="preserve">2025-04-27</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -4531,35 +4531,35 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højen 1</t>
+          <t xml:space="preserve">Møllegade 24</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339669</t>
+          <t xml:space="preserve">7735835</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H76">
-        <v>280</v>
+        <v>969</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">310035291</t>
+          <t xml:space="preserve">311110021</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-16</t>
+          <t xml:space="preserve">2025-04-30</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højen 1</t>
+          <t xml:space="preserve">Peder Skrams Plads 2</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8752</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339669</t>
+          <t xml:space="preserve">4297975</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H77">
-        <v>1320</v>
+        <v>251</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">310035291</t>
+          <t xml:space="preserve">311110012</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-16</t>
+          <t xml:space="preserve">2025-04-30</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterled 1</t>
+          <t xml:space="preserve">Husoddevej 22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642531</t>
+          <t xml:space="preserve">4294467</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4670,16 +4670,16 @@
         </is>
       </c>
       <c r="H78">
-        <v>3753</v>
+        <v>307</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">310037158</t>
+          <t xml:space="preserve">311111614</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-29</t>
+          <t xml:space="preserve">2025-05-08</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7C</t>
+          <t xml:space="preserve">Torstedalle 104</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4721,25 +4721,25 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301856</t>
+          <t xml:space="preserve">4335669</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H79">
-        <v>2172</v>
+        <v>720</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053869</t>
+          <t xml:space="preserve">311114539</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-13</t>
+          <t xml:space="preserve">2025-05-22</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -4771,35 +4771,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 10B</t>
+          <t xml:space="preserve">Torstedalle 108</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">8751</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">100061763</t>
+          <t xml:space="preserve">4335670</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H80">
-        <v>875</v>
+        <v>521</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311056702</t>
+          <t xml:space="preserve">311114537</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-28</t>
+          <t xml:space="preserve">2025-05-22</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langmarksvej 53</t>
+          <t xml:space="preserve">Fortevej 16</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">4293691</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="H81">
-        <v>10244</v>
+        <v>400</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084392</t>
+          <t xml:space="preserve">311114922</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-11-20</t>
+          <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintebakken 145</t>
+          <t xml:space="preserve">Gravengårdsvej 15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4901,25 +4901,25 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8059978</t>
+          <t xml:space="preserve">9438924</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H82">
-        <v>438</v>
+        <v>839</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311109196</t>
+          <t xml:space="preserve">311115261</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-27</t>
+          <t xml:space="preserve">2025-05-27</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -4951,35 +4951,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peder Skrams Plads 2</t>
+          <t xml:space="preserve">Gl Sognevej 8</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">4297975</t>
+          <t xml:space="preserve">7084738</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H83">
-        <v>251</v>
+        <v>346</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110012</t>
+          <t xml:space="preserve">311115807</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-30</t>
+          <t xml:space="preserve">2025-05-29</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5011,35 +5011,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 24</t>
+          <t xml:space="preserve">Gl Sognevej 8</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7735835</t>
+          <t xml:space="preserve">7084738</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H84">
-        <v>969</v>
+        <v>389</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311110021</t>
+          <t xml:space="preserve">311115807</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-30</t>
+          <t xml:space="preserve">2025-05-29</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5071,17 +5071,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Husoddevej 22</t>
+          <t xml:space="preserve">Sogneskellet 30</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">4294467</t>
+          <t xml:space="preserve">4296670</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5090,16 +5090,16 @@
         </is>
       </c>
       <c r="H85">
-        <v>307</v>
+        <v>423</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311111614</t>
+          <t xml:space="preserve">311118783</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-08</t>
+          <t xml:space="preserve">2025-06-12</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5131,17 +5131,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torstedalle 104</t>
+          <t xml:space="preserve">Stationsvej 4</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335669</t>
+          <t xml:space="preserve">8742451</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5150,16 +5150,16 @@
         </is>
       </c>
       <c r="H86">
-        <v>720</v>
+        <v>333</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311114539</t>
+          <t xml:space="preserve">311118789</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-22</t>
+          <t xml:space="preserve">2025-06-12</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5191,17 +5191,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torstedalle 108</t>
+          <t xml:space="preserve">Ny Tønningvej 1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335670</t>
+          <t xml:space="preserve">9683772</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5210,16 +5210,16 @@
         </is>
       </c>
       <c r="H87">
-        <v>521</v>
+        <v>690</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311114537</t>
+          <t xml:space="preserve">311119427</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-22</t>
+          <t xml:space="preserve">2025-06-16</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5251,17 +5251,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fortevej 16</t>
+          <t xml:space="preserve">Fruenshave 1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293691</t>
+          <t xml:space="preserve">4296242</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5270,16 +5270,16 @@
         </is>
       </c>
       <c r="H88">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311114922</t>
+          <t xml:space="preserve">311119615</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-26</t>
+          <t xml:space="preserve">2025-06-17</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5311,35 +5311,35 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gravengårdsvej 15</t>
+          <t xml:space="preserve">Niels Wongesvej 5</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">9438924</t>
+          <t xml:space="preserve">4268541</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H89">
-        <v>839</v>
+        <v>913</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115261</t>
+          <t xml:space="preserve">311119613</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-27</t>
+          <t xml:space="preserve">2025-06-17</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Sognevej 8</t>
+          <t xml:space="preserve">Dronning Ingrids Vej 1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">7084738</t>
+          <t xml:space="preserve">4268442</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H90">
-        <v>346</v>
+        <v>3440</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115807</t>
+          <t xml:space="preserve">311127901</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-29</t>
+          <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Sognevej 8</t>
+          <t xml:space="preserve">Skolestien 1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5441,25 +5441,25 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">7084738</t>
+          <t xml:space="preserve">5640272</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H91">
-        <v>389</v>
+        <v>558</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311115807</t>
+          <t xml:space="preserve">311127895</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-29</t>
+          <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -5491,17 +5491,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sogneskellet 30</t>
+          <t xml:space="preserve">Smedebakken 15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">4296670</t>
+          <t xml:space="preserve">4328112</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -5510,16 +5510,16 @@
         </is>
       </c>
       <c r="H92">
-        <v>423</v>
+        <v>1364</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118783</t>
+          <t xml:space="preserve">311127900</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-12</t>
+          <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -5551,17 +5551,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationsvej 4</t>
+          <t xml:space="preserve">Allegade 13</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">8742451</t>
+          <t xml:space="preserve">5637904</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5570,16 +5570,16 @@
         </is>
       </c>
       <c r="H93">
-        <v>333</v>
+        <v>523</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311118789</t>
+          <t xml:space="preserve">311128478</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-12</t>
+          <t xml:space="preserve">2025-08-11</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -5611,17 +5611,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ny Tønningvej 1</t>
+          <t xml:space="preserve">Borgmesterbakken 26</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">9683772</t>
+          <t xml:space="preserve">5640416</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -5630,16 +5630,16 @@
         </is>
       </c>
       <c r="H94">
-        <v>690</v>
+        <v>1125</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311119427</t>
+          <t xml:space="preserve">311130610</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-16</t>
+          <t xml:space="preserve">2025-08-24</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -5671,17 +5671,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Wongesvej 5</t>
+          <t xml:space="preserve">Skolesvinget 2</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268541</t>
+          <t xml:space="preserve">4335210</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="H95">
-        <v>913</v>
+        <v>340</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">311119613</t>
+          <t xml:space="preserve">311132329</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-17</t>
+          <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fruenshave 1</t>
+          <t xml:space="preserve">Ravnebjerget 10B</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4296242</t>
+          <t xml:space="preserve">4291207</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5750,16 +5750,16 @@
         </is>
       </c>
       <c r="H96">
-        <v>330</v>
+        <v>386</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311119615</t>
+          <t xml:space="preserve">311134644</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-06-17</t>
+          <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Ingrids Vej 1</t>
+          <t xml:space="preserve">Klovenhøjvej 1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268442</t>
+          <t xml:space="preserve">9092406</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5810,16 +5810,16 @@
         </is>
       </c>
       <c r="H97">
-        <v>3440</v>
+        <v>4837</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127901</t>
+          <t xml:space="preserve">311151610</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-06</t>
+          <t xml:space="preserve">2025-12-22</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -5851,35 +5851,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedebakken 15</t>
+          <t xml:space="preserve">Møllevangen 10</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4328112</t>
+          <t xml:space="preserve">8850144</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H98">
-        <v>1364</v>
+        <v>638</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127900</t>
+          <t xml:space="preserve">311152902</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-06</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestien 1</t>
+          <t xml:space="preserve">Møllevangen 4</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640272</t>
+          <t xml:space="preserve">8850144</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5930,16 +5930,16 @@
         </is>
       </c>
       <c r="H99">
-        <v>558</v>
+        <v>638</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311127895</t>
+          <t xml:space="preserve">311152902</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-06</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -5971,35 +5971,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Allegade 13</t>
+          <t xml:space="preserve">Møllevangen 6</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">5637904</t>
+          <t xml:space="preserve">8850144</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H100">
-        <v>523</v>
+        <v>638</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311128478</t>
+          <t xml:space="preserve">311152902</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-11</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6031,35 +6031,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmesterbakken 26</t>
+          <t xml:space="preserve">Møllevangen 8</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640416</t>
+          <t xml:space="preserve">8850144</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H101">
-        <v>1125</v>
+        <v>638</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311130610</t>
+          <t xml:space="preserve">311152902</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-08-24</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 2</t>
+          <t xml:space="preserve">Islandsvej 17</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">4335210</t>
+          <t xml:space="preserve">4327342</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="H102">
-        <v>340</v>
+        <v>2984</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311132329</t>
+          <t xml:space="preserve">311153978</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-02</t>
+          <t xml:space="preserve">2026-01-15</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnebjerget 10B</t>
+          <t xml:space="preserve">Silkeborgvej 145</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4291207</t>
+          <t xml:space="preserve">4301650</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6170,16 +6170,16 @@
         </is>
       </c>
       <c r="H103">
-        <v>386</v>
+        <v>1231</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311134644</t>
+          <t xml:space="preserve">311183741</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-09-15</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6211,35 +6211,35 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klovenhøjvej 1</t>
+          <t xml:space="preserve">Silkeborgvej 145</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9092406</t>
+          <t xml:space="preserve">4301650</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="H104">
-        <v>4837</v>
+        <v>1139</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311151610</t>
+          <t xml:space="preserve">311183741</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-22</t>
+          <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -6271,17 +6271,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 4</t>
+          <t xml:space="preserve">Krokusvej 116</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850144</t>
+          <t xml:space="preserve">9887423</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6290,26 +6290,26 @@
         </is>
       </c>
       <c r="H105">
-        <v>638</v>
+        <v>860</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152902</t>
+          <t xml:space="preserve">311199868</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6331,45 +6331,45 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 6</t>
+          <t xml:space="preserve">Nordrevej 14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850144</t>
+          <t xml:space="preserve">4339928</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H106">
-        <v>638</v>
+        <v>530</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152902</t>
+          <t xml:space="preserve">311199872</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 8</t>
+          <t xml:space="preserve">Østergade 9</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6401,35 +6401,35 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850144</t>
+          <t xml:space="preserve">7904367</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H107">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152902</t>
+          <t xml:space="preserve">311199858</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6451,45 +6451,45 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllevangen 10</t>
+          <t xml:space="preserve">Tyrstedvej 2</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850144</t>
+          <t xml:space="preserve">8154869</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H108">
-        <v>638</v>
+        <v>987</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">311152902</t>
+          <t xml:space="preserve">311200257</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6511,17 +6511,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Islandsvej 17</t>
+          <t xml:space="preserve">Kirkevej 5B</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8751</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4327342</t>
+          <t xml:space="preserve">7840495</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6530,26 +6530,26 @@
         </is>
       </c>
       <c r="H109">
-        <v>2984</v>
+        <v>274</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">311153978</t>
+          <t xml:space="preserve">311202904</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-15</t>
+          <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silkeborgvej 145</t>
+          <t xml:space="preserve">Norgesvej 2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301650</t>
+          <t xml:space="preserve">5647417</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -6590,26 +6590,26 @@
         </is>
       </c>
       <c r="H110">
-        <v>1231</v>
+        <v>1192</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183741</t>
+          <t xml:space="preserve">311207214</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-16</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silkeborgvej 145</t>
+          <t xml:space="preserve">Norgesvej 2</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6641,35 +6641,35 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301650</t>
+          <t xml:space="preserve">5647417</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H111">
-        <v>1139</v>
+        <v>509</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311183741</t>
+          <t xml:space="preserve">311207214</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-16</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordrevej 14</t>
+          <t xml:space="preserve">Norgesvej 2</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6701,25 +6701,25 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339928</t>
+          <t xml:space="preserve">5647417</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H112">
-        <v>530</v>
+        <v>1021</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199872</t>
+          <t xml:space="preserve">311207203</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 9</t>
+          <t xml:space="preserve">Robert Holms Vej 5</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">7904367</t>
+          <t xml:space="preserve">9818698</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6770,16 +6770,16 @@
         </is>
       </c>
       <c r="H113">
-        <v>636</v>
+        <v>1300</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199858</t>
+          <t xml:space="preserve">311207188</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krokusvej 116</t>
+          <t xml:space="preserve">Tværvej 11</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">9887423</t>
+          <t xml:space="preserve">4293955, 100910530</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -6830,16 +6830,16 @@
         </is>
       </c>
       <c r="H114">
-        <v>860</v>
+        <v>254</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199868</t>
+          <t xml:space="preserve">311207192</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -6871,35 +6871,35 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tyrstedvej 2</t>
+          <t xml:space="preserve">Horsensvej 38</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8154869</t>
+          <t xml:space="preserve">4295853</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H115">
-        <v>987</v>
+        <v>2424</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311200257</t>
+          <t xml:space="preserve">311207752</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-13</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -6931,17 +6931,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 5B</t>
+          <t xml:space="preserve">Horsensvej 38B</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8751</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7840495</t>
+          <t xml:space="preserve">8314102</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6950,16 +6950,16 @@
         </is>
       </c>
       <c r="H116">
-        <v>274</v>
+        <v>1055</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311202904</t>
+          <t xml:space="preserve">311207747</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-27</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -6991,17 +6991,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvej 11</t>
+          <t xml:space="preserve">Horsensvej 38</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293955, 100910530</t>
+          <t xml:space="preserve">4295853</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7010,16 +7010,16 @@
         </is>
       </c>
       <c r="H117">
-        <v>254</v>
+        <v>1226</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207192</t>
+          <t xml:space="preserve">311207923</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 2</t>
+          <t xml:space="preserve">Niels Wongesvej 8</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647417</t>
+          <t xml:space="preserve">10130516</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7070,16 +7070,16 @@
         </is>
       </c>
       <c r="H118">
-        <v>1192</v>
+        <v>3110</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207214</t>
+          <t xml:space="preserve">311207985</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 2</t>
+          <t xml:space="preserve">Kildegade 27B</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7121,25 +7121,25 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647417</t>
+          <t xml:space="preserve">5640267</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H119">
-        <v>509</v>
+        <v>438</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207214</t>
+          <t xml:space="preserve">311208851</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norgesvej 2</t>
+          <t xml:space="preserve">Fussingsvej 4</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7181,25 +7181,25 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647417</t>
+          <t xml:space="preserve">5637739</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H120">
-        <v>1021</v>
+        <v>2175</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207203</t>
+          <t xml:space="preserve">311209690</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert Holms Vej 5</t>
+          <t xml:space="preserve">Overholm 2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9818698</t>
+          <t xml:space="preserve">4327922</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -7250,16 +7250,16 @@
         </is>
       </c>
       <c r="H121">
-        <v>1300</v>
+        <v>328</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207188</t>
+          <t xml:space="preserve">311209481</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -7291,35 +7291,35 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsensvej 38</t>
+          <t xml:space="preserve">Sdr. Vissingvej 26B</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295853</t>
+          <t xml:space="preserve">333777, 333778</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H122">
-        <v>2424</v>
+        <v>2559</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207752</t>
+          <t xml:space="preserve">311209730</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -7351,17 +7351,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsensvej 38B</t>
+          <t xml:space="preserve">Søndre Torstedvej 10</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314102</t>
+          <t xml:space="preserve">9982760</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -7370,16 +7370,16 @@
         </is>
       </c>
       <c r="H123">
-        <v>1055</v>
+        <v>3689</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207747</t>
+          <t xml:space="preserve">311220361</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2027-01-03</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -7411,35 +7411,35 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Wongesvej 8</t>
+          <t xml:space="preserve">Ane Staunings Vej 10</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">10130516</t>
+          <t xml:space="preserve">100005723</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H124">
-        <v>3110</v>
+        <v>1200</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207985</t>
+          <t xml:space="preserve">311224671</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -7471,17 +7471,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsensvej 38</t>
+          <t xml:space="preserve">Ane Staunings Vej 4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">4295853</t>
+          <t xml:space="preserve">100005723</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -7490,16 +7490,16 @@
         </is>
       </c>
       <c r="H125">
-        <v>1226</v>
+        <v>501</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311207923</t>
+          <t xml:space="preserve">311224667</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegade 27B</t>
+          <t xml:space="preserve">Ane Staunings Vej 6</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -7541,25 +7541,25 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640267</t>
+          <t xml:space="preserve">100005723</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H126">
-        <v>438</v>
+        <v>1151</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311208851</t>
+          <t xml:space="preserve">311224668</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-27</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overholm 2</t>
+          <t xml:space="preserve">Ane Staunings Vej 8</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -7601,25 +7601,25 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">4327922</t>
+          <t xml:space="preserve">100005723</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H127">
-        <v>328</v>
+        <v>1200</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209481</t>
+          <t xml:space="preserve">311224670</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fussingsvej 4</t>
+          <t xml:space="preserve">Parallelvej 6A</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8751</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5637739</t>
+          <t xml:space="preserve">323774, 323775, 323776</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7670,16 +7670,16 @@
         </is>
       </c>
       <c r="H128">
-        <v>2175</v>
+        <v>1533</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311209690</t>
+          <t xml:space="preserve">311225557</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-31</t>
+          <t xml:space="preserve">2027-01-31</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Torstedvej 10</t>
+          <t xml:space="preserve">Lindvigsvej 10</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9982760</t>
+          <t xml:space="preserve">9722201, 100756152</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7730,16 +7730,16 @@
         </is>
       </c>
       <c r="H129">
-        <v>3689</v>
+        <v>1521</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311220361</t>
+          <t xml:space="preserve">311227856</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-03</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ane Staunings Vej 4</t>
+          <t xml:space="preserve">Lindvigsvej 4</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005723</t>
+          <t xml:space="preserve">8831643</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -7790,16 +7790,16 @@
         </is>
       </c>
       <c r="H130">
-        <v>501</v>
+        <v>6540</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224667</t>
+          <t xml:space="preserve">311227853</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -7831,35 +7831,35 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ane Staunings Vej 6</t>
+          <t xml:space="preserve">Møllegade 20</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8740</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005723</t>
+          <t xml:space="preserve">7735835</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H131">
-        <v>1151</v>
+        <v>1889</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224668</t>
+          <t xml:space="preserve">311229887</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -7891,35 +7891,35 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ane Staunings Vej 8</t>
+          <t xml:space="preserve">Kirkevej 16</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8751</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005723</t>
+          <t xml:space="preserve">4292375</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H132">
-        <v>1200</v>
+        <v>5680</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224670</t>
+          <t xml:space="preserve">311230505</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -7951,35 +7951,35 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ane Staunings Vej 10</t>
+          <t xml:space="preserve">Kirkevej 16</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8751</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">100005723</t>
+          <t xml:space="preserve">4292375</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H133">
-        <v>1200</v>
+        <v>4209</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311224671</t>
+          <t xml:space="preserve">311230504</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-01-26</t>
+          <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindvigsvej 4</t>
+          <t xml:space="preserve">Søndergårdsalle 24</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831643</t>
+          <t xml:space="preserve">8831556</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -8030,16 +8030,16 @@
         </is>
       </c>
       <c r="H134">
-        <v>6540</v>
+        <v>3990</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227853</t>
+          <t xml:space="preserve">311234877</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindvigsvej 10</t>
+          <t xml:space="preserve">Fussingsvej 6</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">9722201, 100756152</t>
+          <t xml:space="preserve">5637742</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -8090,16 +8090,16 @@
         </is>
       </c>
       <c r="H135">
-        <v>1521</v>
+        <v>10292</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311227856</t>
+          <t xml:space="preserve">311254786</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-10</t>
+          <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -8131,35 +8131,35 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 20</t>
+          <t xml:space="preserve">Højballevej 10</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8740</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">7735835</t>
+          <t xml:space="preserve">9980142</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H136">
-        <v>1889</v>
+        <v>372</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311229887</t>
+          <t xml:space="preserve">311290215</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-22</t>
+          <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -8191,35 +8191,35 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 16</t>
+          <t xml:space="preserve">Vandværksvej 32</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8751</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">4292375</t>
+          <t xml:space="preserve">10227122</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H137">
-        <v>5680</v>
+        <v>311</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230499</t>
+          <t xml:space="preserve">311360509</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2029-02-20</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8251,35 +8251,35 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 16</t>
+          <t xml:space="preserve">Langmarksvej 45A</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8751</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4292375</t>
+          <t xml:space="preserve">5642452</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="H138">
-        <v>4209</v>
+        <v>3034</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230499</t>
+          <t xml:space="preserve">311438459</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-02-24</t>
+          <t xml:space="preserve">2030-05-18</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -8311,35 +8311,35 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndergårdsalle 24</t>
+          <t xml:space="preserve">Fruenshave 9</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8732</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831556</t>
+          <t xml:space="preserve">1804662</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="H139">
-        <v>3990</v>
+        <v>252</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311234877</t>
+          <t xml:space="preserve">311458382</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-17</t>
+          <t xml:space="preserve">2030-09-02</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fussingsvej 6</t>
+          <t xml:space="preserve">Bankagervej 99</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -8381,25 +8381,25 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">5637742</t>
+          <t xml:space="preserve">4340275</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="H140">
-        <v>10292</v>
+        <v>720</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254786</t>
+          <t xml:space="preserve">311484004</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-19</t>
+          <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højballevej 10</t>
+          <t xml:space="preserve">Fuglevangsvej 1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8441,25 +8441,25 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">9980142</t>
+          <t xml:space="preserve">5647421</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H141">
-        <v>372</v>
+        <v>1392</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290215</t>
+          <t xml:space="preserve">311531717</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-22</t>
+          <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vandværksvej 32</t>
+          <t xml:space="preserve">Chr M Østergaards Vej 4</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8501,25 +8501,25 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">10227122</t>
+          <t xml:space="preserve">100280264, 100280269, 100280265, 100280266, 100280268</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H142">
-        <v>311</v>
+        <v>36105</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311360509</t>
+          <t xml:space="preserve">311538497</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-20</t>
+          <t xml:space="preserve">2031-07-31</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langmarksvej 45A</t>
+          <t xml:space="preserve">Søvej 3</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -8561,25 +8561,25 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642452</t>
+          <t xml:space="preserve">100302991</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H143">
-        <v>3034</v>
+        <v>1497</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311438459</t>
+          <t xml:space="preserve">311564096</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-18</t>
+          <t xml:space="preserve">2031-11-25</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8611,35 +8611,35 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fruenshave 9</t>
+          <t xml:space="preserve">Endelavevej 16</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8732</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1804662</t>
+          <t xml:space="preserve">5646875</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H144">
-        <v>252</v>
+        <v>1251</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311458382</t>
+          <t xml:space="preserve">311568983</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-09-02</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bankagervej 99</t>
+          <t xml:space="preserve">Højen 1</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -8681,25 +8681,25 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4340275</t>
+          <t xml:space="preserve">4339669</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H145">
-        <v>720</v>
+        <v>8745</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311484004</t>
+          <t xml:space="preserve">311569312</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-18</t>
+          <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevangsvej 1</t>
+          <t xml:space="preserve">Nørrebakken 1</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5647421</t>
+          <t xml:space="preserve">408943, 408944</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8750,16 +8750,16 @@
         </is>
       </c>
       <c r="H146">
-        <v>1392</v>
+        <v>11768</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311531717</t>
+          <t xml:space="preserve">311581729</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-06-28</t>
+          <t xml:space="preserve">2032-03-01</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søvej 3</t>
+          <t xml:space="preserve">Østerhåbsalle 2</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -8801,25 +8801,25 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100302991</t>
+          <t xml:space="preserve">100260046</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H147">
-        <v>1497</v>
+        <v>2044</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311564096</t>
+          <t xml:space="preserve">311592787</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-25</t>
+          <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Endelavevej 16</t>
+          <t xml:space="preserve">Nørretorv 1E</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646875</t>
+          <t xml:space="preserve">322540, 322541</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -8870,16 +8870,16 @@
         </is>
       </c>
       <c r="H148">
-        <v>1251</v>
+        <v>9459</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568983</t>
+          <t xml:space="preserve">311594650</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højen 1</t>
+          <t xml:space="preserve">Enggade 8</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4339669</t>
+          <t xml:space="preserve">5646174</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8930,16 +8930,16 @@
         </is>
       </c>
       <c r="H149">
-        <v>8745</v>
+        <v>430</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311569312</t>
+          <t xml:space="preserve">311618333</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-21</t>
+          <t xml:space="preserve">2032-08-03</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerhåbsalle 2</t>
+          <t xml:space="preserve">Ternevej 66A</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -8981,25 +8981,25 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">100260046</t>
+          <t xml:space="preserve">331936, 331937</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H150">
-        <v>2044</v>
+        <v>6602</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311592787</t>
+          <t xml:space="preserve">311644337</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-12</t>
+          <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggade 8</t>
+          <t xml:space="preserve">Silkeborgvej 245B</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5646174</t>
+          <t xml:space="preserve">332890, 332891</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -9050,16 +9050,16 @@
         </is>
       </c>
       <c r="H151">
-        <v>430</v>
+        <v>3476</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311618333</t>
+          <t xml:space="preserve">311645249</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-03</t>
+          <t xml:space="preserve">2032-11-27</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silkeborgvej 177</t>
+          <t xml:space="preserve">Hybenvej 89</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301565</t>
+          <t xml:space="preserve">5642100</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9650,11 +9650,11 @@
         </is>
       </c>
       <c r="H161">
-        <v>442</v>
+        <v>1847</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738627</t>
+          <t xml:space="preserve">311738637</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Alle 5</t>
+          <t xml:space="preserve">Silkeborgvej 177</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5640942</t>
+          <t xml:space="preserve">4301565</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -9710,11 +9710,11 @@
         </is>
       </c>
       <c r="H162">
-        <v>502</v>
+        <v>442</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738631</t>
+          <t xml:space="preserve">311738627</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenvej 89</t>
+          <t xml:space="preserve">Østre Alle 5</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5642100</t>
+          <t xml:space="preserve">5640942</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -9770,11 +9770,11 @@
         </is>
       </c>
       <c r="H163">
-        <v>1847</v>
+        <v>502</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311738637</t>
+          <t xml:space="preserve">311738631</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østerhåbsalle 1</t>
+          <t xml:space="preserve">Nørrebrogade 38A</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">100035977</t>
+          <t xml:space="preserve">5643101</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -9950,11 +9950,11 @@
         </is>
       </c>
       <c r="H166">
-        <v>900</v>
+        <v>1549</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739352</t>
+          <t xml:space="preserve">311739345</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebrogade 38A</t>
+          <t xml:space="preserve">Østerhåbsalle 1</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5643101</t>
+          <t xml:space="preserve">100035977</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -10010,11 +10010,11 @@
         </is>
       </c>
       <c r="H167">
-        <v>1549</v>
+        <v>900</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311739345</t>
+          <t xml:space="preserve">311739352</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bankagervej 99</t>
+          <t xml:space="preserve">Bankagervej 101</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10486,15 +10486,15 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H175">
-        <v>5113</v>
+        <v>3096</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771128</t>
+          <t xml:space="preserve">311771123</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -10546,15 +10546,15 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H176">
-        <v>3965</v>
+        <v>5113</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771127</t>
+          <t xml:space="preserve">311771128</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bankagervej 101</t>
+          <t xml:space="preserve">Bankagervej 99</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10606,15 +10606,15 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H177">
-        <v>3096</v>
+        <v>3965</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311771123</t>
+          <t xml:space="preserve">311771127</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flintebakken 143</t>
+          <t xml:space="preserve">Brådhusvej 30</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">10098286</t>
+          <t xml:space="preserve">4293715</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -10790,11 +10790,11 @@
         </is>
       </c>
       <c r="H180">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801295</t>
+          <t xml:space="preserve">311801280</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egebjergvej 172</t>
+          <t xml:space="preserve">Bygaden 20</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4287611</t>
+          <t xml:space="preserve">8190251</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -10850,11 +10850,11 @@
         </is>
       </c>
       <c r="H181">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801299</t>
+          <t xml:space="preserve">311801284</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brådhusvej 30</t>
+          <t xml:space="preserve">Dagnæsparken 50</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">4293715</t>
+          <t xml:space="preserve">7938207</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -10910,11 +10910,11 @@
         </is>
       </c>
       <c r="H182">
-        <v>596</v>
+        <v>540</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801280</t>
+          <t xml:space="preserve">311801310</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -10951,17 +10951,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grundtvigsvej 11</t>
+          <t xml:space="preserve">Egebjergvej 172</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8752</t>
+          <t xml:space="preserve">8700</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">4297823</t>
+          <t xml:space="preserve">4287611</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -10970,11 +10970,11 @@
         </is>
       </c>
       <c r="H183">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801290</t>
+          <t xml:space="preserve">311801299</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dagnæsparken 50</t>
+          <t xml:space="preserve">Flintebakken 143</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7938207</t>
+          <t xml:space="preserve">10098286</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -11030,11 +11030,11 @@
         </is>
       </c>
       <c r="H184">
-        <v>540</v>
+        <v>603</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801310</t>
+          <t xml:space="preserve">311801295</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
@@ -11071,17 +11071,17 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 20</t>
+          <t xml:space="preserve">Grundtvigsvej 11</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8700</t>
+          <t xml:space="preserve">8752</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8190251</t>
+          <t xml:space="preserve">4297823</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -11090,11 +11090,11 @@
         </is>
       </c>
       <c r="H185">
-        <v>537</v>
+        <v>560</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801284</t>
+          <t xml:space="preserve">311801290</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Wongesvej 7</t>
+          <t xml:space="preserve">Niels Wongesvej 10</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268440</t>
+          <t xml:space="preserve">4268451</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -11150,11 +11150,11 @@
         </is>
       </c>
       <c r="H186">
-        <v>5883</v>
+        <v>2326</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801400</t>
+          <t xml:space="preserve">311801399</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 11</t>
+          <t xml:space="preserve">Niels Wongesvej 7</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11206,11 +11206,11 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H187">
-        <v>1364</v>
+        <v>5883</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Niels Wongesvej 10</t>
+          <t xml:space="preserve">Skolegade 11</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11261,20 +11261,20 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">4268451</t>
+          <t xml:space="preserve">4268440</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H188">
-        <v>2326</v>
+        <v>1364</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311801399</t>
+          <t xml:space="preserve">311801400</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsensvej 46B</t>
+          <t xml:space="preserve">Horsensvej 46</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11986,11 +11986,11 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H200">
-        <v>1452</v>
+        <v>968</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -12046,11 +12046,11 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H201">
-        <v>968</v>
+        <v>1204</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -12106,11 +12106,11 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H202">
-        <v>1204</v>
+        <v>1386</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Horsensvej 46</t>
+          <t xml:space="preserve">Horsensvej 46B</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12166,11 +12166,11 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="H203">
-        <v>1386</v>
+        <v>1452</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolestien 2A</t>
+          <t xml:space="preserve">Kildegade 25</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -12586,11 +12586,11 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H210">
-        <v>2396</v>
+        <v>285</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -12646,11 +12646,11 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H211">
-        <v>285</v>
+        <v>884</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -12706,11 +12706,11 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H212">
-        <v>884</v>
+        <v>670</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kildegade 25</t>
+          <t xml:space="preserve">Skolestien 2A</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -12766,11 +12766,11 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H213">
-        <v>670</v>
+        <v>2396</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønhøjvej 11B</t>
+          <t xml:space="preserve">Grønhøjvej 1</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12886,15 +12886,15 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H215">
-        <v>346</v>
+        <v>1479</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820707</t>
+          <t xml:space="preserve">311820712</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønhøjvej 1</t>
+          <t xml:space="preserve">Grønhøjvej 11B</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12946,11 +12946,11 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H216">
-        <v>1479</v>
+        <v>346</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Torstedvej 1</t>
+          <t xml:space="preserve">Strandkærvej 89</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4334957</t>
+          <t xml:space="preserve">8831588</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -13070,11 +13070,11 @@
         </is>
       </c>
       <c r="H218">
-        <v>3136</v>
+        <v>1607</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820714</t>
+          <t xml:space="preserve">311820726</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Torstedvej 1</t>
+          <t xml:space="preserve">Strandkærvej 89</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13121,20 +13121,20 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4334957</t>
+          <t xml:space="preserve">8831588</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H219">
-        <v>277</v>
+        <v>2503</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820714</t>
+          <t xml:space="preserve">311820726</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Torstedvej 1</t>
+          <t xml:space="preserve">Strandkærvej 89</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13181,20 +13181,20 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4334957</t>
+          <t xml:space="preserve">8831588</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H220">
-        <v>412</v>
+        <v>1756</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820930</t>
+          <t xml:space="preserve">311820726</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Torstedvej 1</t>
+          <t xml:space="preserve">Strandkærvej 89</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13241,20 +13241,20 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4334957</t>
+          <t xml:space="preserve">8831588</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H221">
-        <v>2123</v>
+        <v>1511</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820714</t>
+          <t xml:space="preserve">311820726</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
@@ -13306,11 +13306,11 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H222">
-        <v>960</v>
+        <v>3136</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -13366,11 +13366,11 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="H223">
-        <v>786</v>
+        <v>277</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -13426,15 +13426,15 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H224">
-        <v>709</v>
+        <v>412</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820714</t>
+          <t xml:space="preserve">311820930</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
@@ -13486,11 +13486,11 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H225">
-        <v>418</v>
+        <v>2123</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -13546,11 +13546,11 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H226">
-        <v>315</v>
+        <v>960</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandkærvej 89</t>
+          <t xml:space="preserve">Søndre Torstedvej 1</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13601,20 +13601,20 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831588</t>
+          <t xml:space="preserve">4334957</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H227">
-        <v>1607</v>
+        <v>786</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820726</t>
+          <t xml:space="preserve">311820714</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandkærvej 89</t>
+          <t xml:space="preserve">Søndre Torstedvej 1</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13661,20 +13661,20 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831588</t>
+          <t xml:space="preserve">4334957</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H228">
-        <v>2503</v>
+        <v>709</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820726</t>
+          <t xml:space="preserve">311820714</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandkærvej 89</t>
+          <t xml:space="preserve">Søndre Torstedvej 1</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13721,20 +13721,20 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831588</t>
+          <t xml:space="preserve">4334957</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H229">
-        <v>1756</v>
+        <v>418</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820726</t>
+          <t xml:space="preserve">311820714</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandkærvej 89</t>
+          <t xml:space="preserve">Søndre Torstedvej 1</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -13781,20 +13781,20 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">8831588</t>
+          <t xml:space="preserve">4334957</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H230">
-        <v>1511</v>
+        <v>315</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820726</t>
+          <t xml:space="preserve">311820714</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821142</t>
+          <t xml:space="preserve">311821143</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5B</t>
+          <t xml:space="preserve">Skolevej 5</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13906,15 +13906,15 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="H232">
-        <v>2844</v>
+        <v>2848</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821142</t>
+          <t xml:space="preserve">311821143</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -13966,11 +13966,11 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="H233">
-        <v>2848</v>
+        <v>298</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -14026,15 +14026,15 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H234">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821142</t>
+          <t xml:space="preserve">311821143</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14086,15 +14086,15 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H235">
-        <v>292</v>
+        <v>386</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821142</t>
+          <t xml:space="preserve">311821143</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14146,15 +14146,15 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H236">
-        <v>386</v>
+        <v>1019</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821142</t>
+          <t xml:space="preserve">311821143</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14206,15 +14206,15 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="H237">
-        <v>1019</v>
+        <v>268</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821142</t>
+          <t xml:space="preserve">311821143</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7A</t>
+          <t xml:space="preserve">Skolevej 5B</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14266,15 +14266,15 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="H238">
-        <v>290</v>
+        <v>2844</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821144</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
@@ -14311,7 +14311,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 5</t>
+          <t xml:space="preserve">Skolevej 7A</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14326,15 +14326,15 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="H239">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821142</t>
+          <t xml:space="preserve">311821144</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 43</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298113</t>
+          <t xml:space="preserve">4298120</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -14750,11 +14750,11 @@
         </is>
       </c>
       <c r="H246">
-        <v>1161</v>
+        <v>1688</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821690</t>
+          <t xml:space="preserve">311821687</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
@@ -14791,7 +14791,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 43A</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14801,20 +14801,20 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298113</t>
+          <t xml:space="preserve">4298120</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H247">
-        <v>544</v>
+        <v>720</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821689</t>
+          <t xml:space="preserve">311821687</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
@@ -14866,11 +14866,11 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H248">
-        <v>1688</v>
+        <v>2292</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Storegade 43</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14921,20 +14921,20 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298120</t>
+          <t xml:space="preserve">4298113</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H249">
-        <v>720</v>
+        <v>1161</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821687</t>
+          <t xml:space="preserve">311821690</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Storegade 43A</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">4298120</t>
+          <t xml:space="preserve">4298113</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -14990,11 +14990,11 @@
         </is>
       </c>
       <c r="H250">
-        <v>2292</v>
+        <v>544</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821687</t>
+          <t xml:space="preserve">311821689</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 9</t>
+          <t xml:space="preserve">Skolegade 7</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -15106,11 +15106,11 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="H252">
-        <v>253</v>
+        <v>860</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -15166,11 +15166,11 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="H253">
-        <v>860</v>
+        <v>1901</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 7</t>
+          <t xml:space="preserve">Skolegade 9</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15226,11 +15226,11 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="H254">
-        <v>1901</v>
+        <v>253</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Ravnebjerget 12</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -15341,20 +15341,20 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4301495</t>
+          <t xml:space="preserve">8742343</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="H256">
-        <v>450</v>
+        <v>561</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823966</t>
+          <t xml:space="preserve">311823872</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -15406,11 +15406,11 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="H257">
-        <v>561</v>
+        <v>1837</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnebjerget 12</t>
+          <t xml:space="preserve">Ravnebjerget 12A</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -15466,11 +15466,11 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="H258">
-        <v>1837</v>
+        <v>1023</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823877</t>
+          <t xml:space="preserve">311823878</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -15631,7 +15631,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnebjerget 12A</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15641,20 +15641,20 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">8742343</t>
+          <t xml:space="preserve">4301495</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="H261">
-        <v>1023</v>
+        <v>450</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823872</t>
+          <t xml:space="preserve">311823966</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830698</t>
+          <t xml:space="preserve">311830697</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">

--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -3294,7 +3294,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053158</t>
+          <t xml:space="preserve">200053157</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">200053159</t>
+          <t xml:space="preserve">200053157</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084316</t>
+          <t xml:space="preserve">311084392</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230505</t>
+          <t xml:space="preserve">311230499</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311230504</t>
+          <t xml:space="preserve">311230499</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311820712</t>
+          <t xml:space="preserve">311820707</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
@@ -13854,7 +13854,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
@@ -14214,7 +14214,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821143</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823878</t>
+          <t xml:space="preserve">311823877</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830697</t>
+          <t xml:space="preserve">311830698</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">

--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L264"/>
+  <dimension ref="A1:M264"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -59,15 +59,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Energimærkningsfirma</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -124,10 +129,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -184,10 +194,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -244,10 +259,15 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -304,10 +324,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -364,10 +389,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -424,10 +454,15 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -484,10 +519,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -544,10 +584,15 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -604,10 +649,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -664,10 +714,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -724,10 +779,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -784,10 +844,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -844,10 +909,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -904,10 +974,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -964,10 +1039,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1024,10 +1104,15 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1084,10 +1169,15 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1144,10 +1234,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1204,10 +1299,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1264,10 +1364,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1324,10 +1429,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1384,10 +1494,15 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1444,10 +1559,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1504,10 +1624,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1564,10 +1689,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1624,10 +1754,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1684,10 +1819,15 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1744,10 +1884,15 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1804,10 +1949,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1864,10 +2014,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1924,10 +2079,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1984,10 +2144,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2044,10 +2209,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2104,10 +2274,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2164,10 +2339,15 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2224,10 +2404,15 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2284,10 +2469,15 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2344,10 +2534,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2404,10 +2599,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2459,15 +2659,20 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt A/S</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2017-12-18</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2519,15 +2724,20 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2018-04-29</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2579,15 +2789,20 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt A/S</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t xml:space="preserve">2018-06-16</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2639,15 +2854,20 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t xml:space="preserve">2018-08-19</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2699,15 +2919,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt A/S</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-06-10</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2759,15 +2984,20 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt A/S</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-08-25</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2819,15 +3049,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek Horsens I/S</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t xml:space="preserve">2019-12-18</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2879,15 +3114,20 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens - Silkeborg P/S</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-08</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2939,15 +3179,20 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens - Silkeborg P/S</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t xml:space="preserve">2020-06-15</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -2999,15 +3244,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Rambøll Danmark A/S (Ålborg)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-03-31</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3059,15 +3309,20 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-04-14</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3119,15 +3374,20 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-05-26</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3179,15 +3439,20 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-06-28</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3239,15 +3504,20 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-09-01</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3299,15 +3569,20 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-09-22</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3359,15 +3634,20 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-09-22</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3419,15 +3699,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-09-27</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3479,15 +3764,20 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-09-27</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3539,15 +3829,20 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiMidt</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-09-27</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3599,15 +3894,20 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t xml:space="preserve">2021-10-12</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3659,15 +3959,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-01-03</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3719,15 +4024,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-02-14</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3779,15 +4089,20 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-09-13</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3839,15 +4154,20 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-10-01</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3899,15 +4219,20 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-10-01</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -3959,15 +4284,20 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-11-14</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4019,15 +4349,20 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t xml:space="preserve">2022-11-30</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4079,15 +4414,20 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t xml:space="preserve">H17 Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4139,15 +4479,20 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t xml:space="preserve">H17 Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4199,15 +4544,20 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
+          <t xml:space="preserve">H17 Ingeniørfirma ApS</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-16</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4259,15 +4609,20 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning Aps</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t xml:space="preserve">2023-04-29</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4319,15 +4674,20 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-05-13</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4379,15 +4739,20 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t xml:space="preserve">factum2 Horsens</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-05-28</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4439,15 +4804,20 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t xml:space="preserve">AURA Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t xml:space="preserve">2024-11-20</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4499,15 +4869,20 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-04-27</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4559,15 +4934,20 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-04-30</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4619,15 +4999,20 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-04-30</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4679,15 +5064,20 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-08</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4739,15 +5129,20 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-22</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4799,15 +5194,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-22</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4859,15 +5259,20 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-26</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4919,15 +5324,20 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-27</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -4979,15 +5389,20 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-29</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5039,15 +5454,20 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-05-29</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5099,15 +5519,20 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-12</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5159,15 +5584,20 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-12</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5219,15 +5649,20 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-16</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5279,15 +5714,20 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-17</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5339,15 +5779,20 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-06-17</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5399,15 +5844,20 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5459,15 +5909,20 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5519,15 +5974,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-06</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5579,15 +6039,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-11</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5639,15 +6104,20 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-08-24</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5699,15 +6169,20 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-02</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5759,15 +6234,20 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-09-15</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5819,15 +6299,20 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
           <t xml:space="preserve">2025-12-22</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5879,15 +6364,20 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5939,15 +6429,20 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -5999,15 +6494,20 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6059,15 +6559,20 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6119,15 +6624,20 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
+          <t xml:space="preserve">TREFOR Energi A/S</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-01-15</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6179,15 +6689,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning Aps</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6239,15 +6754,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning Aps</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-06-16</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -6299,15 +6819,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6359,15 +6884,20 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6419,15 +6949,20 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6479,15 +7014,20 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-13</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6539,15 +7079,20 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-27</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6599,15 +7144,20 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6659,15 +7209,20 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6719,15 +7274,20 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6779,15 +7339,20 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6839,15 +7404,20 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6899,15 +7469,20 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -6959,15 +7534,20 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7019,15 +7599,20 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7079,15 +7664,20 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7139,15 +7729,20 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7199,15 +7794,20 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7259,15 +7859,20 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7319,15 +7924,20 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-31</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7379,15 +7989,20 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-03</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7439,15 +8054,20 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7499,15 +8119,20 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7559,15 +8184,20 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="L126" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="M126" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7619,15 +8249,20 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-26</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="L127" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr">
+      <c r="M127" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7679,15 +8314,20 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-01-31</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="L128" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="M128" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7739,15 +8379,20 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="L129" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="M129" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7799,15 +8444,20 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-10</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="L130" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="M130" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7859,15 +8509,20 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-22</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="L131" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
+      <c r="M131" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7919,15 +8574,20 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="L132" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="M132" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -7979,15 +8639,20 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-02-24</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="L133" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr">
+      <c r="M133" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8039,15 +8704,20 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-03-17</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="L134" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="M134" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8099,15 +8769,20 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
+          <t xml:space="preserve">EWII Energi A/S</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-06-19</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="L135" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="M135" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8159,15 +8834,20 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning Aps</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-12-22</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="L136" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
+      <c r="M136" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8219,15 +8899,20 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
+          <t xml:space="preserve">Factum2 A/S</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
           <t xml:space="preserve">2029-02-20</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8279,15 +8964,20 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
+          <t xml:space="preserve">BYGTEST ApS</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-05-18</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="L138" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="M138" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8339,15 +9029,20 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-09-02</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="L139" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="M139" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8399,15 +9094,20 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
+          <t xml:space="preserve">Factum2 A/S</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-18</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8459,15 +9159,20 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
+          <t xml:space="preserve">Factum2 A/S</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-06-28</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="L141" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="M141" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8519,15 +9224,20 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
+          <t xml:space="preserve">Norconsult A/S</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-07-31</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="L142" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
+      <c r="M142" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8579,15 +9289,20 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-11-25</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="L143" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
+      <c r="M143" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8639,15 +9354,20 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="L144" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="M144" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8699,15 +9419,20 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="L145" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
+      <c r="M145" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8759,15 +9484,20 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-03-01</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="L146" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
+      <c r="M146" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8819,15 +9549,20 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-12</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="L147" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
+      <c r="M147" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8879,15 +9614,20 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-04-22</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="L148" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="M148" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8939,15 +9679,20 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-08-03</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -8999,15 +9744,20 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
+          <t xml:space="preserve">Inspec ApS</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-23</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="L150" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="M150" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9059,15 +9809,20 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-11-27</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="L151" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="M151" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9119,15 +9874,20 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-03-07</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="L152" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="M152" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9179,15 +9939,20 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="L153" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="M153" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9239,15 +10004,20 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="L154" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr">
+      <c r="M154" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9299,15 +10069,20 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="L155" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
+      <c r="M155" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9359,15 +10134,20 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="L156" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L156" t="inlineStr">
+      <c r="M156" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9419,15 +10199,20 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="L157" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr">
+      <c r="M157" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9479,15 +10264,20 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="L158" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
+      <c r="M158" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9539,15 +10329,20 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
           <t xml:space="preserve">2033-11-29</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="L159" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="M159" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9599,15 +10394,20 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-02</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="L160" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
+      <c r="M160" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9659,15 +10459,20 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="L161" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
+      <c r="M161" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9719,15 +10524,20 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9779,15 +10589,20 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-13</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="L163" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
+      <c r="M163" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9839,15 +10654,20 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-14</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="L164" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="M164" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9899,15 +10719,20 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-15</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="L165" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
+      <c r="M165" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -9959,15 +10784,20 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="L166" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="M166" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10019,15 +10849,20 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-16</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="L167" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="M167" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10079,15 +10914,20 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-21</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="L168" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
+      <c r="M168" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10139,15 +10979,20 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="L169" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
+      <c r="M169" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10199,15 +11044,20 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-02-23</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="L170" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
+      <c r="M170" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10259,15 +11109,20 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-01</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="L171" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
+      <c r="M171" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10319,15 +11174,20 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="L172" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
+      <c r="M172" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10379,15 +11239,20 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-03-06</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="L173" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr">
+      <c r="M173" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10439,15 +11304,20 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-04-16</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="L174" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr">
+      <c r="M174" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10499,15 +11369,20 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="L175" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L175" t="inlineStr">
+      <c r="M175" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10559,15 +11434,20 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="L176" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L176" t="inlineStr">
+      <c r="M176" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10619,15 +11499,20 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="L177" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr">
+      <c r="M177" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10679,15 +11564,20 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
+          <t xml:space="preserve">Botjek A/S</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-07-03</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="L178" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="M178" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10739,15 +11629,20 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-03</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="L179" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr">
+      <c r="M179" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10799,15 +11694,20 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10859,15 +11759,20 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10919,15 +11824,20 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="L182" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="M182" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -10979,15 +11889,20 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="L183" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="M183" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11039,15 +11954,20 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="L184" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
+      <c r="M184" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11099,15 +12019,20 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-05</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11159,15 +12084,20 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-06</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="L186" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="M186" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11219,15 +12149,20 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-06</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="L187" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="M187" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11279,15 +12214,20 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-06</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="L188" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
+      <c r="M188" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11339,15 +12279,20 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-10</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="L189" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="M189" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11399,15 +12344,20 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-10</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="L190" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="M190" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11459,15 +12409,20 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-17</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="L191" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
+      <c r="M191" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11519,15 +12474,20 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-17</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="L192" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
+      <c r="M192" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11579,15 +12539,20 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="L193" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="M193" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11639,15 +12604,20 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
           <t xml:space="preserve">2034-12-18</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11699,15 +12669,20 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
+          <t xml:space="preserve">Dansk Boligtjek ApS</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-01-29</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="L195" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
+      <c r="M195" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11759,15 +12734,20 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-07</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="L196" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
+      <c r="M196" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11819,15 +12799,20 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-13</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="L197" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
+      <c r="M197" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11879,15 +12864,20 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-02-13</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="L198" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="M198" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11939,15 +12929,20 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="L199" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="M199" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -11999,15 +12994,20 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12059,15 +13059,20 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="L201" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
+      <c r="M201" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12119,15 +13124,20 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="L202" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="M202" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12179,15 +13189,20 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-20</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="L203" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
+      <c r="M203" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12239,15 +13254,20 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="L204" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="M204" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12299,15 +13319,20 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="L205" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
+      <c r="M205" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12359,15 +13384,20 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="L206" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr">
+      <c r="M206" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12419,15 +13449,20 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="L207" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr">
+      <c r="M207" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12479,15 +13514,20 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="L208" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr">
+      <c r="M208" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12539,15 +13579,20 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="L209" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr">
+      <c r="M209" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12599,15 +13644,20 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="L210" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr">
+      <c r="M210" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12659,15 +13709,20 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="L211" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr">
+      <c r="M211" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12719,15 +13774,20 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="L212" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr">
+      <c r="M212" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12779,15 +13839,20 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-24</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="L213" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr">
+      <c r="M213" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12839,15 +13904,20 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="L214" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr">
+      <c r="M214" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12899,15 +13969,20 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="L215" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr">
+      <c r="M215" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -12959,15 +14034,20 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="L216" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
+      <c r="M216" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13019,15 +14099,20 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="L217" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
+      <c r="M217" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13079,15 +14164,20 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="L218" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
+      <c r="M218" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13139,15 +14229,20 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="L219" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
+      <c r="M219" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13199,15 +14294,20 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="L220" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
+      <c r="M220" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13259,15 +14359,20 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="L221" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="M221" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13319,15 +14424,20 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="L222" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
+      <c r="M222" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13379,15 +14489,20 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="L223" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="M223" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13439,15 +14554,20 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="L224" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="M224" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13499,15 +14619,20 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="L225" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
+      <c r="M225" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13559,15 +14684,20 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="L226" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
+      <c r="M226" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13619,15 +14749,20 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="L227" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
+      <c r="M227" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13679,15 +14814,20 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="L228" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
+      <c r="M228" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13739,15 +14879,20 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="L229" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
+      <c r="M229" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13799,15 +14944,20 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sandager Bygge- &amp; Energirådgivning ApS</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-27</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="L230" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr">
+      <c r="M230" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13859,15 +15009,20 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="L231" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr">
+      <c r="M231" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13919,15 +15074,20 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="L232" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr">
+      <c r="M232" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -13979,15 +15139,20 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="L233" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr">
+      <c r="M233" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14039,15 +15204,20 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="L234" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr">
+      <c r="M234" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14099,15 +15269,20 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="L235" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr">
+      <c r="M235" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14159,15 +15334,20 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="L236" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr">
+      <c r="M236" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14219,15 +15399,20 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="L237" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr">
+      <c r="M237" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14279,15 +15464,20 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="L238" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr">
+      <c r="M238" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14339,15 +15529,20 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="L239" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
+      <c r="M239" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14399,15 +15594,20 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="L240" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
+      <c r="M240" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14459,15 +15659,20 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="L241" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr">
+      <c r="M241" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14519,15 +15724,20 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="L242" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr">
+      <c r="M242" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14579,15 +15789,20 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="L243" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr">
+      <c r="M243" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14639,15 +15854,20 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="L244" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
+      <c r="M244" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14699,15 +15919,20 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="L245" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
+      <c r="M245" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14759,15 +15984,20 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="L246" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
+      <c r="M246" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14819,15 +16049,20 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
+      <c r="L247" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
+      <c r="M247" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14879,15 +16114,20 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
+      <c r="L248" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
+      <c r="M248" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14939,15 +16179,20 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="L249" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
+      <c r="M249" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -14999,15 +16244,20 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-03-31</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
+      <c r="L250" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
+      <c r="M250" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15059,15 +16309,20 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
+      <c r="M251" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15119,15 +16374,20 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="L252" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
+      <c r="M252" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15179,15 +16439,20 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="L253" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr">
+      <c r="M253" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15239,15 +16504,20 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-01</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="L254" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr">
+      <c r="M254" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15299,15 +16569,20 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-07</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
+      <c r="L255" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
+      <c r="M255" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15354,20 +16629,25 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823872</t>
+          <t xml:space="preserve">311823877</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
+      <c r="L256" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
+      <c r="M256" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15414,20 +16694,25 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823872</t>
+          <t xml:space="preserve">311823877</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="L257" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
+      <c r="M257" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15474,20 +16759,25 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823872</t>
+          <t xml:space="preserve">311823877</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
+      <c r="L258" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
+      <c r="M258" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15539,15 +16829,20 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
+      <c r="L259" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
+      <c r="M259" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15599,15 +16894,20 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="L260" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
+      <c r="M260" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15659,15 +16959,20 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
+          <t xml:space="preserve">DAI A/S</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-04-09</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="L261" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr">
+      <c r="M261" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15719,15 +17024,20 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="L262" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr">
+      <c r="M262" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15779,15 +17089,20 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-09</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="L263" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr">
+      <c r="M263" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -15839,21 +17154,26 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">2035-05-21</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="L264" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr">
+      <c r="M264" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L264"/>
+  <autoFilter ref="A1:M264"/>
 </worksheet>
 </file>
--- a/public/exports/29189889.xlsx
+++ b/public/exports/29189889.xlsx
@@ -4669,12 +4669,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053869</t>
+          <t xml:space="preserve">311053859</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">factum2 Horsens</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">311084392</t>
+          <t xml:space="preserve">311084316</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821144</t>
+          <t xml:space="preserve">311821142</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823877</t>
+          <t xml:space="preserve">311823872</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
@@ -16694,7 +16694,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823877</t>
+          <t xml:space="preserve">311823872</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16759,7 +16759,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311823877</t>
+          <t xml:space="preserve">311823872</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
@@ -17084,12 +17084,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311830698</t>
+          <t xml:space="preserve">311830697</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
